--- a/Colchester_CT_Budget_Analysis.xlsx
+++ b/Colchester_CT_Budget_Analysis.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Inflation &amp; Population" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Regional Comparison" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Demographic Peers" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="ECS Analysis" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="260">
   <si>
     <t xml:space="preserve">Town of Colchester, CT - Adopted Budget Analysis (FY 2007-08 to FY 2024-25)</t>
   </si>
@@ -704,13 +705,135 @@
   </si>
   <si>
     <t xml:space="preserve">Colchester has the LOWEST per capita spending among all demographic peer towns with available data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECS (Education Cost Sharing) Funding Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colchester, CT — FY 2007-08 through FY 2024-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: Adopted Budget PDFs, CT State Dept of Education, BLS CPI-U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 1: ECS Revenue History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual ECS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPI Index
+(2008=100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflation-Adj
+ECS (from FY08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual Gap
+vs Inflation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative Gap
+vs Inflation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECS as %
+of BOE Budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YoY ECS
+Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 2: Key Findings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak ECS Funding (FY 2013-14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current ECS Funding (FY 2024-25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nominal Decline from Peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Decline from Peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflation-Adjusted ECS Should Be (FY 24-25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Purchasing Power Loss vs FY 07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative Gap (All Years Sum)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECS Share of BOE: FY 07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECS Share of BOE: FY 24-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECS Share Decline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years ECS Frozen at Current Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3: Cumulative Loss from Peak (FY 2013-14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak ECS
+(FY 13-14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPI Adjustment
+Factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflation-Adj
+Peak ECS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual Loss
+vs Adj Peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative
+Loss from Peak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL CUMULATIVE LOSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• FY 2010-11 ECS was reduced due to state budget cuts; $1.93M was offset by Federal ARRA stimulus funds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Colchester is classified as "overfunded" under the ECS formula and has been "held harmless" since FY 2020-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• The CT Conference of Municipalities estimates $820M in missed inflationary adjustments statewide since 2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• FY 2023-24 ECS assumed same as FY 2022-23 based on hold-harmless provision; no separate budget PDF available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• CPI-U data from Bureau of Labor Statistics; FY 2024-25 uses projected 2025 CPI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
@@ -720,8 +843,11 @@
     <numFmt numFmtId="170" formatCode="#,##0"/>
     <numFmt numFmtId="171" formatCode="0"/>
     <numFmt numFmtId="172" formatCode="\$#,##0"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="174" formatCode="0.0&quot;pp&quot;"/>
+    <numFmt numFmtId="175" formatCode="0.000"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -940,8 +1066,57 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFC0504D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -957,7 +1132,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFE8F5E9"/>
+        <bgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -984,8 +1159,32 @@
         <bgColor rgb="FFF0FDF4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF0070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+        <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0504D"/>
+        <bgColor rgb="FF993366"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1009,6 +1208,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="double"/>
+      <bottom style="double"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1035,7 +1241,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="132">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1424,47 +1630,143 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="26" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="35" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1493,10 +1795,10 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFC0504D"/>
       <rgbColor rgb="FFF0FDF4"/>
       <rgbColor rgb="FFE8F5E9"/>
       <rgbColor rgb="FF660066"/>
@@ -1512,14 +1814,14 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFD9E1F2"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD6E4F0"/>
+      <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF4472C4"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
@@ -2522,6 +2824,1247 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I60"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="102" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="103" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="104" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="105" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+    </row>
+    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="106" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="106" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="106" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" s="106" t="s">
+        <v>229</v>
+      </c>
+      <c r="E6" s="106" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6" s="106" t="s">
+        <v>231</v>
+      </c>
+      <c r="G6" s="106" t="s">
+        <v>232</v>
+      </c>
+      <c r="H6" s="106" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="106" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="108" t="n">
+        <v>12976438</v>
+      </c>
+      <c r="C7" s="109" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="110" t="n">
+        <f aca="false">B7</f>
+        <v>12976438</v>
+      </c>
+      <c r="E7" s="111" t="n">
+        <f aca="false">B7-D7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="111" t="n">
+        <f aca="false">E7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="112" t="n">
+        <f aca="false">B7/H7</f>
+        <v>0.367671542126339</v>
+      </c>
+      <c r="H7" s="108" t="n">
+        <v>35293561</v>
+      </c>
+      <c r="I7" s="107" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="113" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="114" t="n">
+        <v>13547231</v>
+      </c>
+      <c r="C8" s="115" t="n">
+        <v>99.6</v>
+      </c>
+      <c r="D8" s="116" t="n">
+        <f aca="false">B7*(C8/C7)</f>
+        <v>12924532.248</v>
+      </c>
+      <c r="E8" s="117" t="n">
+        <f aca="false">B8-D8</f>
+        <v>622698.752</v>
+      </c>
+      <c r="F8" s="117" t="n">
+        <f aca="false">F7+E8</f>
+        <v>622698.752</v>
+      </c>
+      <c r="G8" s="118" t="n">
+        <f aca="false">B8/H8</f>
+        <v>0.373036750996996</v>
+      </c>
+      <c r="H8" s="114" t="n">
+        <v>36316076</v>
+      </c>
+      <c r="I8" s="118" t="n">
+        <f aca="false">(B8-B7)/B7</f>
+        <v>0.043986878371399</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="107" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="108" t="n">
+        <v>13547231</v>
+      </c>
+      <c r="C9" s="109" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="D9" s="110" t="n">
+        <f aca="false">B7*(C9/C7)</f>
+        <v>13145131.694</v>
+      </c>
+      <c r="E9" s="111" t="n">
+        <f aca="false">B9-D9</f>
+        <v>402099.306000002</v>
+      </c>
+      <c r="F9" s="111" t="n">
+        <f aca="false">F8+E9</f>
+        <v>1024798.058</v>
+      </c>
+      <c r="G9" s="112" t="n">
+        <f aca="false">B9/H9</f>
+        <v>0.367612633686729</v>
+      </c>
+      <c r="H9" s="108" t="n">
+        <v>36851919</v>
+      </c>
+      <c r="I9" s="112" t="n">
+        <f aca="false">(B9-B8)/B8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="114" t="n">
+        <v>11614515</v>
+      </c>
+      <c r="C10" s="115" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="D10" s="116" t="n">
+        <f aca="false">B7*(C10/C7)</f>
+        <v>13560377.71</v>
+      </c>
+      <c r="E10" s="117" t="n">
+        <f aca="false">B10-D10</f>
+        <v>-1945862.71</v>
+      </c>
+      <c r="F10" s="117" t="n">
+        <f aca="false">F9+E10</f>
+        <v>-921064.651999997</v>
+      </c>
+      <c r="G10" s="118" t="n">
+        <f aca="false">B10/H10</f>
+        <v>0.317065661485145</v>
+      </c>
+      <c r="H10" s="114" t="n">
+        <v>36631261</v>
+      </c>
+      <c r="I10" s="118" t="n">
+        <f aca="false">(B10-B9)/B9</f>
+        <v>-0.142665021361192</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="108" t="n">
+        <v>13547231</v>
+      </c>
+      <c r="C11" s="109" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="D11" s="110" t="n">
+        <f aca="false">B7*(C11/C7)</f>
+        <v>13832882.908</v>
+      </c>
+      <c r="E11" s="111" t="n">
+        <f aca="false">B11-D11</f>
+        <v>-285651.907999998</v>
+      </c>
+      <c r="F11" s="111" t="n">
+        <f aca="false">F10+E11</f>
+        <v>-1206716.56</v>
+      </c>
+      <c r="G11" s="112" t="n">
+        <f aca="false">B11/H11</f>
+        <v>0.367839814099475</v>
+      </c>
+      <c r="H11" s="108" t="n">
+        <v>36829159</v>
+      </c>
+      <c r="I11" s="112" t="n">
+        <f aca="false">(B11-B10)/B10</f>
+        <v>0.166405226563485</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="113" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="114" t="n">
+        <v>13723859</v>
+      </c>
+      <c r="C12" s="115" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="D12" s="116" t="n">
+        <f aca="false">B7*(C12/C7)</f>
+        <v>14040505.916</v>
+      </c>
+      <c r="E12" s="117" t="n">
+        <f aca="false">B12-D12</f>
+        <v>-316646.916000001</v>
+      </c>
+      <c r="F12" s="117" t="n">
+        <f aca="false">F11+E12</f>
+        <v>-1523363.476</v>
+      </c>
+      <c r="G12" s="118" t="n">
+        <f aca="false">B12/H12</f>
+        <v>0.365681669716887</v>
+      </c>
+      <c r="H12" s="114" t="n">
+        <v>37529524</v>
+      </c>
+      <c r="I12" s="118" t="n">
+        <f aca="false">(B12-B11)/B11</f>
+        <v>0.0130379411113607</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="107" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="108" t="n">
+        <v>13773810</v>
+      </c>
+      <c r="C13" s="109" t="n">
+        <v>110</v>
+      </c>
+      <c r="D13" s="110" t="n">
+        <f aca="false">B7*(C13/C7)</f>
+        <v>14274081.8</v>
+      </c>
+      <c r="E13" s="111" t="n">
+        <f aca="false">B13-D13</f>
+        <v>-500271.800000001</v>
+      </c>
+      <c r="F13" s="111" t="n">
+        <f aca="false">F12+E13</f>
+        <v>-2023635.276</v>
+      </c>
+      <c r="G13" s="112" t="n">
+        <f aca="false">B13/H13</f>
+        <v>0.352499461416183</v>
+      </c>
+      <c r="H13" s="108" t="n">
+        <v>39074698</v>
+      </c>
+      <c r="I13" s="112" t="n">
+        <f aca="false">(B13-B12)/B12</f>
+        <v>0.00363971970274542</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="114" t="n">
+        <v>13761528</v>
+      </c>
+      <c r="C14" s="115" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="D14" s="116" t="n">
+        <f aca="false">B7*(C14/C7)</f>
+        <v>14287058.238</v>
+      </c>
+      <c r="E14" s="117" t="n">
+        <f aca="false">B14-D14</f>
+        <v>-525530.238</v>
+      </c>
+      <c r="F14" s="117" t="n">
+        <f aca="false">F13+E14</f>
+        <v>-2549165.514</v>
+      </c>
+      <c r="G14" s="118" t="n">
+        <f aca="false">B14/H14</f>
+        <v>0.347069312487141</v>
+      </c>
+      <c r="H14" s="114" t="n">
+        <v>39650662</v>
+      </c>
+      <c r="I14" s="118" t="n">
+        <f aca="false">(B14-B13)/B13</f>
+        <v>-0.000891692276864571</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="108" t="n">
+        <v>13761528</v>
+      </c>
+      <c r="C15" s="109" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="D15" s="110" t="n">
+        <f aca="false">B7*(C15/C7)</f>
+        <v>14468728.37</v>
+      </c>
+      <c r="E15" s="111" t="n">
+        <f aca="false">B15-D15</f>
+        <v>-707200.369999999</v>
+      </c>
+      <c r="F15" s="111" t="n">
+        <f aca="false">F14+E15</f>
+        <v>-3256365.884</v>
+      </c>
+      <c r="G15" s="112" t="n">
+        <f aca="false">B15/H15</f>
+        <v>0.345723602562492</v>
+      </c>
+      <c r="H15" s="108" t="n">
+        <v>39805000</v>
+      </c>
+      <c r="I15" s="112" t="n">
+        <f aca="false">(B15-B14)/B14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="113" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="114" t="n">
+        <v>13591055</v>
+      </c>
+      <c r="C16" s="115" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="D16" s="116" t="n">
+        <f aca="false">B7*(C16/C7)</f>
+        <v>14767186.444</v>
+      </c>
+      <c r="E16" s="117" t="n">
+        <f aca="false">B16-D16</f>
+        <v>-1176131.444</v>
+      </c>
+      <c r="F16" s="117" t="n">
+        <f aca="false">F15+E16</f>
+        <v>-4432497.32799999</v>
+      </c>
+      <c r="G16" s="118" t="n">
+        <f aca="false">B16/H16</f>
+        <v>0.342309465041306</v>
+      </c>
+      <c r="H16" s="114" t="n">
+        <v>39704000</v>
+      </c>
+      <c r="I16" s="118" t="n">
+        <f aca="false">(B16-B15)/B15</f>
+        <v>-0.012387650557409</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="107" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="108" t="n">
+        <v>13503310</v>
+      </c>
+      <c r="C17" s="109" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="D17" s="110" t="n">
+        <f aca="false">B7*(C17/C7)</f>
+        <v>15130526.708</v>
+      </c>
+      <c r="E17" s="111" t="n">
+        <f aca="false">B17-D17</f>
+        <v>-1627216.708</v>
+      </c>
+      <c r="F17" s="111" t="n">
+        <f aca="false">F16+E17</f>
+        <v>-6059714.03599999</v>
+      </c>
+      <c r="G17" s="112" t="n">
+        <f aca="false">B17/H17</f>
+        <v>0.33232372701991</v>
+      </c>
+      <c r="H17" s="108" t="n">
+        <v>40633000</v>
+      </c>
+      <c r="I17" s="112" t="n">
+        <f aca="false">(B17-B16)/B16</f>
+        <v>-0.00645608453501218</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="114" t="n">
+        <v>12670601</v>
+      </c>
+      <c r="C18" s="115" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="D18" s="116" t="n">
+        <f aca="false">B7*(C18/C7)</f>
+        <v>15403031.906</v>
+      </c>
+      <c r="E18" s="117" t="n">
+        <f aca="false">B18-D18</f>
+        <v>-2732430.906</v>
+      </c>
+      <c r="F18" s="117" t="n">
+        <f aca="false">F17+E18</f>
+        <v>-8792144.94199999</v>
+      </c>
+      <c r="G18" s="118" t="n">
+        <f aca="false">B18/H18</f>
+        <v>0.312530240244685</v>
+      </c>
+      <c r="H18" s="114" t="n">
+        <v>40542000</v>
+      </c>
+      <c r="I18" s="118" t="n">
+        <f aca="false">(B18-B17)/B17</f>
+        <v>-0.061667028306393</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="108" t="n">
+        <v>12359179</v>
+      </c>
+      <c r="C19" s="109" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="D19" s="110" t="n">
+        <f aca="false">B7*(C19/C7)</f>
+        <v>15597678.476</v>
+      </c>
+      <c r="E19" s="111" t="n">
+        <f aca="false">B19-D19</f>
+        <v>-3238499.476</v>
+      </c>
+      <c r="F19" s="111" t="n">
+        <f aca="false">F18+E19</f>
+        <v>-12030644.418</v>
+      </c>
+      <c r="G19" s="112" t="n">
+        <f aca="false">B19/H19</f>
+        <v>0.299718183140945</v>
+      </c>
+      <c r="H19" s="108" t="n">
+        <v>41236000</v>
+      </c>
+      <c r="I19" s="112" t="n">
+        <f aca="false">(B19-B18)/B18</f>
+        <v>-0.0245783132149769</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="114" t="n">
+        <v>12040218</v>
+      </c>
+      <c r="C20" s="115" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="D20" s="116" t="n">
+        <f aca="false">B7*(C20/C7)</f>
+        <v>16337335.442</v>
+      </c>
+      <c r="E20" s="117" t="n">
+        <f aca="false">B20-D20</f>
+        <v>-4297117.442</v>
+      </c>
+      <c r="F20" s="117" t="n">
+        <f aca="false">F19+E20</f>
+        <v>-16327761.86</v>
+      </c>
+      <c r="G20" s="118" t="n">
+        <f aca="false">B20/H20</f>
+        <v>0.291460130718954</v>
+      </c>
+      <c r="H20" s="114" t="n">
+        <v>41310000</v>
+      </c>
+      <c r="I20" s="118" t="n">
+        <f aca="false">(B20-B19)/B19</f>
+        <v>-0.025807620392908</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="107" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="108" t="n">
+        <v>12040218</v>
+      </c>
+      <c r="C21" s="109" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="D21" s="110" t="n">
+        <f aca="false">B7*(C21/C7)</f>
+        <v>17634979.242</v>
+      </c>
+      <c r="E21" s="111" t="n">
+        <f aca="false">B21-D21</f>
+        <v>-5594761.242</v>
+      </c>
+      <c r="F21" s="111" t="n">
+        <f aca="false">F20+E21</f>
+        <v>-21922523.102</v>
+      </c>
+      <c r="G21" s="112" t="n">
+        <f aca="false">B21/H21</f>
+        <v>0.286583152833647</v>
+      </c>
+      <c r="H21" s="108" t="n">
+        <v>42013000</v>
+      </c>
+      <c r="I21" s="112" t="n">
+        <f aca="false">(B21-B20)/B20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="114" t="n">
+        <v>12040218</v>
+      </c>
+      <c r="C22" s="115" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="D22" s="116" t="n">
+        <f aca="false">B7*(C22/C7)</f>
+        <v>18361659.77</v>
+      </c>
+      <c r="E22" s="117" t="n">
+        <f aca="false">B22-D22</f>
+        <v>-6321441.77</v>
+      </c>
+      <c r="F22" s="117" t="n">
+        <f aca="false">F21+E22</f>
+        <v>-28243964.872</v>
+      </c>
+      <c r="G22" s="118" t="n">
+        <f aca="false">B22/H22</f>
+        <v>0.278934738793004</v>
+      </c>
+      <c r="H22" s="114" t="n">
+        <v>43165000</v>
+      </c>
+      <c r="I22" s="118" t="n">
+        <f aca="false">(B22-B21)/B21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="107" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="108" t="n">
+        <v>12040218</v>
+      </c>
+      <c r="C23" s="109" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="D23" s="110" t="n">
+        <f aca="false">B7*(C23/C7)</f>
+        <v>18828811.538</v>
+      </c>
+      <c r="E23" s="111" t="n">
+        <f aca="false">B23-D23</f>
+        <v>-6788593.538</v>
+      </c>
+      <c r="F23" s="111" t="n">
+        <f aca="false">F22+E23</f>
+        <v>-35032558.41</v>
+      </c>
+      <c r="G23" s="112" t="n">
+        <f aca="false">B23/H23</f>
+        <v>0.270566696629214</v>
+      </c>
+      <c r="H23" s="108" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="I23" s="112" t="n">
+        <f aca="false">(B23-B22)/B22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="114" t="n">
+        <v>12040218</v>
+      </c>
+      <c r="C24" s="115" t="n">
+        <v>148</v>
+      </c>
+      <c r="D24" s="116" t="n">
+        <f aca="false">B7*(C24/C7)</f>
+        <v>19205128.24</v>
+      </c>
+      <c r="E24" s="117" t="n">
+        <f aca="false">B24-D24</f>
+        <v>-7164910.24</v>
+      </c>
+      <c r="F24" s="117" t="n">
+        <f aca="false">F23+E24</f>
+        <v>-42197468.65</v>
+      </c>
+      <c r="G24" s="118" t="n">
+        <f aca="false">B24/H24</f>
+        <v>0.264039868421053</v>
+      </c>
+      <c r="H24" s="114" t="n">
+        <v>45600000</v>
+      </c>
+      <c r="I24" s="118" t="n">
+        <f aca="false">(B24-B23)/B23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="105" t="s">
+        <v>235</v>
+      </c>
+      <c r="B26" s="105"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="105"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="119" t="s">
+        <v>236</v>
+      </c>
+      <c r="B27" s="110" t="n">
+        <f aca="false">MAX(B7:B24)</f>
+        <v>13773810</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="119" t="s">
+        <v>237</v>
+      </c>
+      <c r="B28" s="110" t="n">
+        <f aca="false">B24</f>
+        <v>12040218</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="119" t="s">
+        <v>238</v>
+      </c>
+      <c r="B29" s="111" t="n">
+        <f aca="false">B24-MAX(B7:B24)</f>
+        <v>-1733592</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="119" t="s">
+        <v>239</v>
+      </c>
+      <c r="B30" s="112" t="n">
+        <f aca="false">(B24-MAX(B7:B24))/MAX(B7:B24)</f>
+        <v>-0.125861471880329</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="119" t="s">
+        <v>240</v>
+      </c>
+      <c r="B31" s="110" t="n">
+        <f aca="false">D24</f>
+        <v>19205128.24</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="119" t="s">
+        <v>241</v>
+      </c>
+      <c r="B32" s="111" t="n">
+        <f aca="false">F24</f>
+        <v>-42197468.65</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="119" t="s">
+        <v>242</v>
+      </c>
+      <c r="B33" s="111" t="n">
+        <f aca="false">SUM(E7:E24)</f>
+        <v>-42197468.65</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="119" t="s">
+        <v>243</v>
+      </c>
+      <c r="B34" s="112" t="n">
+        <f aca="false">G7</f>
+        <v>0.367671542126339</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="B35" s="112" t="n">
+        <f aca="false">G24</f>
+        <v>0.264039868421053</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="119" t="s">
+        <v>245</v>
+      </c>
+      <c r="B36" s="120" t="n">
+        <f aca="false">G24-G7</f>
+        <v>-0.103631673705286</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="119" t="s">
+        <v>246</v>
+      </c>
+      <c r="B37" s="121" t="n">
+        <f aca="false">COUNTIF(B7:B24,B24)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="105" t="s">
+        <v>247</v>
+      </c>
+      <c r="B39" s="105"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="105"/>
+      <c r="G39" s="105"/>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+    </row>
+    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="122" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" s="122" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="122" t="s">
+        <v>248</v>
+      </c>
+      <c r="D40" s="122" t="s">
+        <v>249</v>
+      </c>
+      <c r="E40" s="122" t="s">
+        <v>250</v>
+      </c>
+      <c r="F40" s="122" t="s">
+        <v>251</v>
+      </c>
+      <c r="G40" s="122" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="107" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="123" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="C41" s="110" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D41" s="124" t="n">
+        <f aca="false">C13/C13</f>
+        <v>1</v>
+      </c>
+      <c r="E41" s="110" t="n">
+        <f aca="false">C41*D41</f>
+        <v>13773810</v>
+      </c>
+      <c r="F41" s="111" t="n">
+        <f aca="false">B41-E41</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="111" t="n">
+        <f aca="false">F41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="125" t="n">
+        <f aca="false">B14</f>
+        <v>13761528</v>
+      </c>
+      <c r="C42" s="116" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D42" s="126" t="n">
+        <f aca="false">C14/C13</f>
+        <v>1.00090909090909</v>
+      </c>
+      <c r="E42" s="116" t="n">
+        <f aca="false">C42*D42</f>
+        <v>13786331.6454545</v>
+      </c>
+      <c r="F42" s="117" t="n">
+        <f aca="false">B42-E42</f>
+        <v>-24803.6454545427</v>
+      </c>
+      <c r="G42" s="117" t="n">
+        <f aca="false">G41+F42</f>
+        <v>-24803.6454545427</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="123" t="n">
+        <f aca="false">B15</f>
+        <v>13761528</v>
+      </c>
+      <c r="C43" s="110" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D43" s="124" t="n">
+        <f aca="false">C15/C13</f>
+        <v>1.01363636363636</v>
+      </c>
+      <c r="E43" s="110" t="n">
+        <f aca="false">C43*D43</f>
+        <v>13961634.6818182</v>
+      </c>
+      <c r="F43" s="111" t="n">
+        <f aca="false">B43-E43</f>
+        <v>-200106.681818182</v>
+      </c>
+      <c r="G43" s="111" t="n">
+        <f aca="false">G42+F43</f>
+        <v>-224910.327272724</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="113" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="125" t="n">
+        <f aca="false">B16</f>
+        <v>13591055</v>
+      </c>
+      <c r="C44" s="116" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D44" s="126" t="n">
+        <f aca="false">C16/C13</f>
+        <v>1.03454545454545</v>
+      </c>
+      <c r="E44" s="116" t="n">
+        <f aca="false">C44*D44</f>
+        <v>14249632.5272727</v>
+      </c>
+      <c r="F44" s="117" t="n">
+        <f aca="false">B44-E44</f>
+        <v>-658577.527272726</v>
+      </c>
+      <c r="G44" s="117" t="n">
+        <f aca="false">G43+F44</f>
+        <v>-883487.85454545</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="107" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="123" t="n">
+        <f aca="false">B17</f>
+        <v>13503310</v>
+      </c>
+      <c r="C45" s="110" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D45" s="124" t="n">
+        <f aca="false">C17/C13</f>
+        <v>1.06</v>
+      </c>
+      <c r="E45" s="110" t="n">
+        <f aca="false">C45*D45</f>
+        <v>14600238.6</v>
+      </c>
+      <c r="F45" s="111" t="n">
+        <f aca="false">B45-E45</f>
+        <v>-1096928.6</v>
+      </c>
+      <c r="G45" s="111" t="n">
+        <f aca="false">G44+F45</f>
+        <v>-1980416.45454545</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" s="125" t="n">
+        <f aca="false">B18</f>
+        <v>12670601</v>
+      </c>
+      <c r="C46" s="116" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D46" s="126" t="n">
+        <f aca="false">C18/C13</f>
+        <v>1.07909090909091</v>
+      </c>
+      <c r="E46" s="116" t="n">
+        <f aca="false">C46*D46</f>
+        <v>14863193.1545455</v>
+      </c>
+      <c r="F46" s="117" t="n">
+        <f aca="false">B46-E46</f>
+        <v>-2192592.15454545</v>
+      </c>
+      <c r="G46" s="117" t="n">
+        <f aca="false">G45+F46</f>
+        <v>-4173008.60909091</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="123" t="n">
+        <f aca="false">B19</f>
+        <v>12359179</v>
+      </c>
+      <c r="C47" s="110" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D47" s="124" t="n">
+        <f aca="false">C19/C13</f>
+        <v>1.09272727272727</v>
+      </c>
+      <c r="E47" s="110" t="n">
+        <f aca="false">C47*D47</f>
+        <v>15051017.8363636</v>
+      </c>
+      <c r="F47" s="111" t="n">
+        <f aca="false">B47-E47</f>
+        <v>-2691838.83636364</v>
+      </c>
+      <c r="G47" s="111" t="n">
+        <f aca="false">G46+F47</f>
+        <v>-6864847.44545454</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="125" t="n">
+        <f aca="false">B20</f>
+        <v>12040218</v>
+      </c>
+      <c r="C48" s="116" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D48" s="126" t="n">
+        <f aca="false">C20/C13</f>
+        <v>1.14454545454545</v>
+      </c>
+      <c r="E48" s="116" t="n">
+        <f aca="false">C48*D48</f>
+        <v>15764751.6272727</v>
+      </c>
+      <c r="F48" s="117" t="n">
+        <f aca="false">B48-E48</f>
+        <v>-3724533.62727273</v>
+      </c>
+      <c r="G48" s="117" t="n">
+        <f aca="false">G47+F48</f>
+        <v>-10589381.0727273</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="107" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" s="123" t="n">
+        <f aca="false">B21</f>
+        <v>12040218</v>
+      </c>
+      <c r="C49" s="110" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D49" s="124" t="n">
+        <f aca="false">C21/C13</f>
+        <v>1.23545454545455</v>
+      </c>
+      <c r="E49" s="110" t="n">
+        <f aca="false">C49*D49</f>
+        <v>17016916.1727273</v>
+      </c>
+      <c r="F49" s="111" t="n">
+        <f aca="false">B49-E49</f>
+        <v>-4976698.17272728</v>
+      </c>
+      <c r="G49" s="111" t="n">
+        <f aca="false">G48+F49</f>
+        <v>-15566079.2454545</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50" s="125" t="n">
+        <f aca="false">B22</f>
+        <v>12040218</v>
+      </c>
+      <c r="C50" s="116" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D50" s="126" t="n">
+        <f aca="false">C22/C13</f>
+        <v>1.28636363636364</v>
+      </c>
+      <c r="E50" s="116" t="n">
+        <f aca="false">C50*D50</f>
+        <v>17718128.3181818</v>
+      </c>
+      <c r="F50" s="117" t="n">
+        <f aca="false">B50-E50</f>
+        <v>-5677910.31818182</v>
+      </c>
+      <c r="G50" s="117" t="n">
+        <f aca="false">G49+F50</f>
+        <v>-21243989.5636364</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="107" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" s="123" t="n">
+        <f aca="false">B23</f>
+        <v>12040218</v>
+      </c>
+      <c r="C51" s="110" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D51" s="124" t="n">
+        <f aca="false">C23/C13</f>
+        <v>1.31909090909091</v>
+      </c>
+      <c r="E51" s="110" t="n">
+        <f aca="false">C51*D51</f>
+        <v>18168907.5545455</v>
+      </c>
+      <c r="F51" s="111" t="n">
+        <f aca="false">B51-E51</f>
+        <v>-6128689.55454546</v>
+      </c>
+      <c r="G51" s="111" t="n">
+        <f aca="false">G50+F51</f>
+        <v>-27372679.1181818</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="125" t="n">
+        <f aca="false">B24</f>
+        <v>12040218</v>
+      </c>
+      <c r="C52" s="116" t="n">
+        <f aca="false">B13</f>
+        <v>13773810</v>
+      </c>
+      <c r="D52" s="126" t="n">
+        <f aca="false">C24/C13</f>
+        <v>1.34545454545455</v>
+      </c>
+      <c r="E52" s="116" t="n">
+        <f aca="false">C52*D52</f>
+        <v>18532035.2727273</v>
+      </c>
+      <c r="F52" s="117" t="n">
+        <f aca="false">B52-E52</f>
+        <v>-6491817.27272727</v>
+      </c>
+      <c r="G52" s="117" t="n">
+        <f aca="false">G51+F52</f>
+        <v>-33864496.3909091</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="127" t="s">
+        <v>253</v>
+      </c>
+      <c r="B53" s="128"/>
+      <c r="C53" s="128"/>
+      <c r="D53" s="128"/>
+      <c r="E53" s="128"/>
+      <c r="F53" s="129" t="n">
+        <f aca="false">SUM(F41:F52)</f>
+        <v>-33864496.3909091</v>
+      </c>
+      <c r="G53" s="129" t="n">
+        <f aca="false">G52</f>
+        <v>-33864496.3909091</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="130" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="131" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="131" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="131" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="131" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="131" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A39:I39"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -8086,17 +9629,17 @@
       <c r="G36" s="85"/>
       <c r="H36" s="85"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="97" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="64" t="s">
         <v>212</v>
       </c>
-      <c r="B39" s="97"/>
-      <c r="C39" s="97"/>
-      <c r="D39" s="97"/>
-      <c r="E39" s="97"/>
-      <c r="F39" s="97"/>
-    </row>
-    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="64"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+    </row>
+    <row r="40" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="66" t="s">
         <v>89</v>
       </c>
@@ -8116,21 +9659,21 @@
         <v>215</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="67" t="s">
         <v>139</v>
       </c>
       <c r="B41" s="69" t="n">
         <v>15752</v>
       </c>
-      <c r="C41" s="98" t="n">
+      <c r="C41" s="70" t="n">
         <v>62678131</v>
       </c>
-      <c r="D41" s="99" t="n">
+      <c r="D41" s="71" t="n">
         <f aca="false">C41/B41</f>
         <v>3979.05859573388</v>
       </c>
-      <c r="E41" s="100" t="n">
+      <c r="E41" s="97" t="n">
         <f aca="false">D41/D41-1</f>
         <v>0</v>
       </c>
@@ -8138,21 +9681,21 @@
         <v>216</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="73" t="s">
         <v>179</v>
       </c>
       <c r="B42" s="75" t="n">
         <v>16571</v>
       </c>
-      <c r="C42" s="101" t="n">
+      <c r="C42" s="76" t="n">
         <v>71200000</v>
       </c>
-      <c r="D42" s="102" t="n">
+      <c r="D42" s="77" t="n">
         <f aca="false">C42/B42</f>
         <v>4296.66284472874</v>
       </c>
-      <c r="E42" s="103" t="n">
+      <c r="E42" s="98" t="n">
         <f aca="false">D42/D41-1</f>
         <v>0.0798189424341189</v>
       </c>
@@ -8160,21 +9703,21 @@
         <v>217</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="73" t="s">
         <v>141</v>
       </c>
       <c r="B43" s="75" t="n">
         <v>13109</v>
       </c>
-      <c r="C43" s="101" t="n">
+      <c r="C43" s="76" t="n">
         <v>56700000</v>
       </c>
-      <c r="D43" s="102" t="n">
+      <c r="D43" s="77" t="n">
         <f aca="false">C43/B43</f>
         <v>4325.27271340301</v>
       </c>
-      <c r="E43" s="103" t="n">
+      <c r="E43" s="98" t="n">
         <f aca="false">D43/D41-1</f>
         <v>0.0870090523523133</v>
       </c>
@@ -8182,21 +9725,21 @@
         <v>218</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="73" t="s">
         <v>186</v>
       </c>
       <c r="B44" s="75" t="n">
         <v>15575</v>
       </c>
-      <c r="C44" s="101" t="n">
+      <c r="C44" s="76" t="n">
         <v>67400000</v>
       </c>
-      <c r="D44" s="102" t="n">
+      <c r="D44" s="77" t="n">
         <f aca="false">C44/B44</f>
         <v>4327.44783306581</v>
       </c>
-      <c r="E44" s="103" t="n">
+      <c r="E44" s="98" t="n">
         <f aca="false">D44/D41-1</f>
         <v>0.0875556941296263</v>
       </c>
@@ -8204,21 +9747,21 @@
         <v>219</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="73" t="s">
         <v>180</v>
       </c>
       <c r="B45" s="75" t="n">
         <v>14502</v>
       </c>
-      <c r="C45" s="101" t="n">
+      <c r="C45" s="76" t="n">
         <v>63666000</v>
       </c>
-      <c r="D45" s="102" t="n">
+      <c r="D45" s="77" t="n">
         <f aca="false">C45/B45</f>
         <v>4390.15308233347</v>
       </c>
-      <c r="E45" s="103" t="n">
+      <c r="E45" s="98" t="n">
         <f aca="false">D45/D41-1</f>
         <v>0.103314509376753</v>
       </c>
@@ -8226,28 +9769,28 @@
         <v>220</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="104" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="81" t="s">
         <v>221</v>
       </c>
-      <c r="D46" s="105" t="n">
+      <c r="D46" s="99" t="n">
         <f aca="false">AVERAGE(D42:D45)</f>
         <v>4334.88411838276</v>
       </c>
-      <c r="E46" s="106" t="n">
+      <c r="E46" s="100" t="n">
         <f aca="false">D46/D41-1</f>
         <v>0.0894245495732027</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="107" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="101" t="s">
         <v>222</v>
       </c>
-      <c r="B48" s="107"/>
-      <c r="C48" s="107"/>
-      <c r="D48" s="107"/>
-      <c r="E48" s="107"/>
-      <c r="F48" s="107"/>
+      <c r="B48" s="101"/>
+      <c r="C48" s="101"/>
+      <c r="D48" s="101"/>
+      <c r="E48" s="101"/>
+      <c r="F48" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="14">

--- a/Colchester_CT_Budget_Analysis.xlsx
+++ b/Colchester_CT_Budget_Analysis.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Regional Comparison" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Demographic Peers" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="ECS Analysis" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Staffing &amp; Salary Analysis" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="371">
   <si>
     <t xml:space="preserve">Town of Colchester, CT - Adopted Budget Analysis (FY 2007-08 to FY 2024-25)</t>
   </si>
@@ -827,6 +828,371 @@
   </si>
   <si>
     <t xml:space="preserve">• CPI-U data from Bureau of Labor Statistics; FY 2024-25 uses projected 2025 CPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staffing &amp; Salary Analysis — Colchester BOE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY 2008-09 through FY 2024-25 | Sources: CT EdSight, NCES, Budget PDFs, CT TRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: EdSight verified data available for FY 2019-20 and FY 2022-23 through 2024-25. Earlier years estimated from enrollment trends and NCES ratios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 1: Enrollment, Staffing, and Ratios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student
+Enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teacher
+FTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin
+FTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students
+per Teacher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students
+per Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin per
+100 Teachers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg Teacher
+Salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg Admin
+Salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin/Teacher
+Salary Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOE Cost
+per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin as %
+of Teachers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrollment Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teacher FTE Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin FTE Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teacher Salary Growth (total)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Salary Growth (total)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOE Cost per Student Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students per Teacher: FY 08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students per Teacher: FY 24-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students per Admin: FY 08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students per Admin: FY 24-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admins per 100 Teachers: FY 08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admins per 100 Teachers: FY 24-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOE Cost per Student: FY 08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOE Cost per Student: FY 24-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3: EdSight Verified Staffing Detail (Official CT DOE Data)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gen Ed Teachers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec Ed Teachers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Teachers (classroom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gen Ed Paraprofessionals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec Ed Paraprofessionals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin - Central Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin - School Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Administrators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instructional Specialists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counselors/SW/Psychologists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School Nurses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Library/Media (Certified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Non-Instructional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student-Teacher Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Sources &amp; Notes:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• EdSight verified data: CT State Dept of Education, public-edsight.ct.gov/educators/fte-staffing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Enrollment data: Extracted directly from Colchester adopted budget PDFs (town profile pages)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• FY 2012-13 through 2015-16 enrollment interpolated between 3,210 (FY 2011-12) and 2,727 (FY 2016-17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Teacher FTE for years before FY 2019-20 estimated from enrollment trends and CT avg student-teacher ratios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Average teacher salary: FY 2018-19 from CT TRS data ($78,804), FY 2022-23 from Niche.com ($82,554)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Average admin salary estimated from Salary.com benchmarks and GovSalaries.com data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• "Administrators" includes central office admins, coordinators, dept chairs, and school-level admins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Admin FTE variability between years may reflect reclassification of positions (coordinators vs specialists)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Colchester BOE highest individual salary in 2024: $96,130 (GovSalaries.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• CT statewide average teacher salary: $86,511 (connecticut.teach.org)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECTION 4: STAFFING DATA — VERIFIED FROM CT EDSIGHT FTE STAFFING CSV REPORTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gen Ed
+Teachers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sped
+Teachers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total
+Teachers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School
+Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central
+Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Admin
+(Narrow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instr.
+Specialists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin+Spec
+(Broad)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S/T
+Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S/A Ratio
+(Narrow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School verified (CSV); central office estimated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All verified (EdSight CSV + district report)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change (FY 08-09 → FY 24-25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Sources:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Teachers (Gen Ed + Sped), School Admin, Instructional Specialists: CT EdSight FTE Staffing CSV Reports (all 17 years verified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Central Office Admin: EdSight district aggregate reports (verified FY 19-20 = 4.0, FY 22-23 onward = 2.8; pre-2019 estimated ~4.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Enrollment: Town of Colchester Adopted Budget documents (town profile sections)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue text with green background = verified from official source. Gray italic = estimated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School-level admin = principals, assistant principals, department chairs. Central office = superintendent, asst supt, directors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instructional specialists = literacy coaches, math coaches, curriculum coordinators, data specialists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECTION 5: SPECIAL EDUCATION STAFFING — VERIFIED FROM CT EDSIGHT FTE STAFFING CSV REPORTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sped
+Paras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total
+Sped Staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gen Ed
+Paras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counselors
+/Psych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nurses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total
+Staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sped %
+of Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key Findings:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Sped teachers: 26.5 → 28.0 FTE (+5.7%) — essentially flat despite enrollment declining 31.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Sped paraprofessionals: 50.0 → 65.0 FTE (+30%) — the largest growth area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Total sped staff: 76.5 → 93.0 FTE (+21.6%) while enrollment dropped 31.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Sped as % of total staff: grew from 17.4% to 19.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• This reflects federal/state mandates (IDEA) — sped services are driven by IEP needs, not enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠ FY 24-25 Gen Ed Paraprofessionals jumped from 33 to 89 FTE — may reflect reclassification, not actual hiring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All data from CT EdSight FTE Staffing CSV Reports (verified for all 17 years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECTION 6: TOWN INSURANCE COSTS — EXTRACTED FROM ADOPTED BUDGET LINE ITEMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health
+Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Town
+Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Town
+Budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance as
+% of Budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health Ins
+(CPI-Adj)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change (FY 07-08 → FY 24-25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Town health insurance grew 54.1% ($729K → $1.12M) — roughly tracking CPI inflation (51.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Total town insurance grew 61.5% ($1.25M → $2.02M) — workers' comp drove the gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Insurance as % of town budget rose from 7.4% to 9.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Multiple plan design renegotiations produced savings in FY 12-13, FY 14-15, and FY 15-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• BOE employee benefits were $4.49M (13.5% of BOE budget) in FY 07-08 — detailed breakdown not available for later years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• FY 23-24 total insurance interpolated (budget PDF not available for that year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health insurance amounts from budget comparison tables and adopted budget line items (Code 41211).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total insurance includes: health, workers' compensation, property/liability, and unemployment.</t>
   </si>
 </sst>
 </file>
@@ -842,12 +1208,12 @@
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="#,##0"/>
     <numFmt numFmtId="171" formatCode="0"/>
-    <numFmt numFmtId="172" formatCode="\$#,##0"/>
-    <numFmt numFmtId="173" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="174" formatCode="0.0&quot;pp&quot;"/>
-    <numFmt numFmtId="175" formatCode="0.000"/>
+    <numFmt numFmtId="172" formatCode="0.0&quot;pp&quot;"/>
+    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="174" formatCode="0.00\x"/>
+    <numFmt numFmtId="175" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1115,8 +1481,84 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF999999"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF999999"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF5B21B6"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF94A3B8"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF64748B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF16A34A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF475569"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF991B1B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF854D0E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1144,7 +1586,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1A365D"/>
-        <bgColor rgb="FF333333"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
@@ -1156,7 +1598,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
-        <bgColor rgb="FFF0FDF4"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1168,7 +1610,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF0070C0"/>
+        <bgColor rgb="FF64748B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1180,7 +1622,43 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0504D"/>
-        <bgColor rgb="FF993366"/>
+        <bgColor rgb="FFDC2626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
+        <bgColor rgb="FF666666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8B0000"/>
+        <bgColor rgb="FF800000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF2F2"/>
+        <bgColor rgb="FFFFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF854D0E"/>
+        <bgColor rgb="FFC0504D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFBEB"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1241,7 +1719,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="173">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1650,19 +2128,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1670,63 +2148,63 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1734,39 +2212,203 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="35" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="35" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="33" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="33" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="16" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1789,17 +2431,17 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF8B0000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF548235"/>
+      <rgbColor rgb="FF5B21B6"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFD9E1F2"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF666666"/>
+      <rgbColor rgb="FF94A3B8"/>
       <rgbColor rgb="FFC0504D"/>
-      <rgbColor rgb="FFF0FDF4"/>
+      <rgbColor rgb="FFFFFBEB"/>
       <rgbColor rgb="FFE8F5E9"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -1814,29 +2456,29 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFF0FDF4"/>
+      <rgbColor rgb="FFE2EFDA"/>
+      <rgbColor rgb="FFFEF2F2"/>
       <rgbColor rgb="FFD6E4F0"/>
-      <rgbColor rgb="FFD9E2F3"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FF4472C4"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666666"/>
+      <rgbColor rgb="FF64748B"/>
       <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF1A365D"/>
       <rgbColor rgb="FF16A34A"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF991B1B"/>
+      <rgbColor rgb="FF854D0E"/>
       <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF475569"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -2832,28 +3474,28 @@
   <dimension ref="A1:I60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="102" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="103" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="104" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="105" t="s">
         <v>226</v>
       </c>
@@ -2866,7 +3508,7 @@
       <c r="H5" s="105"/>
       <c r="I5" s="105"/>
     </row>
-    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="106" t="s">
         <v>1</v>
       </c>
@@ -2895,7 +3537,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="107" t="s">
         <v>12</v>
       </c>
@@ -2928,7 +3570,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="113" t="s">
         <v>13</v>
       </c>
@@ -2962,7 +3604,7 @@
         <v>0.043986878371399</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="107" t="s">
         <v>14</v>
       </c>
@@ -2996,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="113" t="s">
         <v>15</v>
       </c>
@@ -3030,7 +3672,7 @@
         <v>-0.142665021361192</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="107" t="s">
         <v>16</v>
       </c>
@@ -3064,7 +3706,7 @@
         <v>0.166405226563485</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="113" t="s">
         <v>17</v>
       </c>
@@ -3098,7 +3740,7 @@
         <v>0.0130379411113607</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="107" t="s">
         <v>18</v>
       </c>
@@ -3132,7 +3774,7 @@
         <v>0.00363971970274542</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="113" t="s">
         <v>19</v>
       </c>
@@ -3166,7 +3808,7 @@
         <v>-0.000891692276864571</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="107" t="s">
         <v>20</v>
       </c>
@@ -3200,7 +3842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="113" t="s">
         <v>21</v>
       </c>
@@ -3234,7 +3876,7 @@
         <v>-0.012387650557409</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="107" t="s">
         <v>22</v>
       </c>
@@ -3268,7 +3910,7 @@
         <v>-0.00645608453501218</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="113" t="s">
         <v>23</v>
       </c>
@@ -3302,7 +3944,7 @@
         <v>-0.061667028306393</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="107" t="s">
         <v>24</v>
       </c>
@@ -3336,7 +3978,7 @@
         <v>-0.0245783132149769</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
@@ -3370,7 +4012,7 @@
         <v>-0.025807620392908</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="107" t="s">
         <v>26</v>
       </c>
@@ -3404,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="113" t="s">
         <v>27</v>
       </c>
@@ -3438,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="107" t="s">
         <v>28</v>
       </c>
@@ -3472,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="113" t="s">
         <v>30</v>
       </c>
@@ -3506,7 +4148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="105" t="s">
         <v>235</v>
       </c>
@@ -3519,7 +4161,7 @@
       <c r="H26" s="105"/>
       <c r="I26" s="105"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="119" t="s">
         <v>236</v>
       </c>
@@ -3528,7 +4170,7 @@
         <v>13773810</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="119" t="s">
         <v>237</v>
       </c>
@@ -3537,7 +4179,7 @@
         <v>12040218</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="119" t="s">
         <v>238</v>
       </c>
@@ -3546,7 +4188,7 @@
         <v>-1733592</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="119" t="s">
         <v>239</v>
       </c>
@@ -3555,7 +4197,7 @@
         <v>-0.125861471880329</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="119" t="s">
         <v>240</v>
       </c>
@@ -3564,7 +4206,7 @@
         <v>19205128.24</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="119" t="s">
         <v>241</v>
       </c>
@@ -3573,7 +4215,7 @@
         <v>-42197468.65</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="119" t="s">
         <v>242</v>
       </c>
@@ -3582,7 +4224,7 @@
         <v>-42197468.65</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="119" t="s">
         <v>243</v>
       </c>
@@ -3591,7 +4233,7 @@
         <v>0.367671542126339</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="119" t="s">
         <v>244</v>
       </c>
@@ -3600,7 +4242,7 @@
         <v>0.264039868421053</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="119" t="s">
         <v>245</v>
       </c>
@@ -3609,7 +4251,7 @@
         <v>-0.103631673705286</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="119" t="s">
         <v>246</v>
       </c>
@@ -3618,7 +4260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="105" t="s">
         <v>247</v>
       </c>
@@ -3631,7 +4273,7 @@
       <c r="H39" s="105"/>
       <c r="I39" s="105"/>
     </row>
-    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="122" t="s">
         <v>1</v>
       </c>
@@ -3654,7 +4296,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="107" t="s">
         <v>18</v>
       </c>
@@ -3683,7 +4325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="113" t="s">
         <v>19</v>
       </c>
@@ -3712,7 +4354,7 @@
         <v>-24803.6454545427</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="107" t="s">
         <v>20</v>
       </c>
@@ -3741,7 +4383,7 @@
         <v>-224910.327272724</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="113" t="s">
         <v>21</v>
       </c>
@@ -3770,7 +4412,7 @@
         <v>-883487.85454545</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="107" t="s">
         <v>22</v>
       </c>
@@ -3799,7 +4441,7 @@
         <v>-1980416.45454545</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="113" t="s">
         <v>23</v>
       </c>
@@ -3828,7 +4470,7 @@
         <v>-4173008.60909091</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="107" t="s">
         <v>24</v>
       </c>
@@ -3857,7 +4499,7 @@
         <v>-6864847.44545454</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="113" t="s">
         <v>25</v>
       </c>
@@ -3886,7 +4528,7 @@
         <v>-10589381.0727273</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="107" t="s">
         <v>26</v>
       </c>
@@ -3915,7 +4557,7 @@
         <v>-15566079.2454545</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="113" t="s">
         <v>27</v>
       </c>
@@ -3944,7 +4586,7 @@
         <v>-21243989.5636364</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="107" t="s">
         <v>28</v>
       </c>
@@ -3973,7 +4615,7 @@
         <v>-27372679.1181818</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="113" t="s">
         <v>30</v>
       </c>
@@ -4002,7 +4644,7 @@
         <v>-33864496.3909091</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="127" t="s">
         <v>253</v>
       </c>
@@ -4019,32 +4661,32 @@
         <v>-33864496.3909091</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="130" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="131" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="131" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="131" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="131" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="131" t="s">
         <v>259</v>
       </c>
@@ -4054,6 +4696,3642 @@
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A39:I39"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:N169"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="42"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="102" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="132" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="133" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="105" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+    </row>
+    <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="106" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="106" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="106" t="s">
+        <v>265</v>
+      </c>
+      <c r="D6" s="106" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" s="106" t="s">
+        <v>267</v>
+      </c>
+      <c r="F6" s="106" t="s">
+        <v>268</v>
+      </c>
+      <c r="G6" s="106" t="s">
+        <v>269</v>
+      </c>
+      <c r="H6" s="106" t="s">
+        <v>270</v>
+      </c>
+      <c r="I6" s="106" t="s">
+        <v>271</v>
+      </c>
+      <c r="J6" s="106" t="s">
+        <v>272</v>
+      </c>
+      <c r="K6" s="106" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="106" t="s">
+        <v>273</v>
+      </c>
+      <c r="M6" s="106" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="134" t="n">
+        <v>3267</v>
+      </c>
+      <c r="C7" s="109" t="n">
+        <v>237</v>
+      </c>
+      <c r="D7" s="109" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="135" t="n">
+        <f aca="false">B7/C7</f>
+        <v>13.7848101265823</v>
+      </c>
+      <c r="F7" s="135" t="n">
+        <f aca="false">B7/D7</f>
+        <v>233.357142857143</v>
+      </c>
+      <c r="G7" s="135" t="n">
+        <f aca="false">D7/C7*100</f>
+        <v>5.90717299578059</v>
+      </c>
+      <c r="H7" s="108" t="n">
+        <v>64500</v>
+      </c>
+      <c r="I7" s="108" t="n">
+        <v>95000</v>
+      </c>
+      <c r="J7" s="136" t="n">
+        <f aca="false">I7/H7</f>
+        <v>1.47286821705426</v>
+      </c>
+      <c r="K7" s="108" t="n">
+        <v>36316076</v>
+      </c>
+      <c r="L7" s="110" t="n">
+        <f aca="false">K7/B7</f>
+        <v>11116.0318334864</v>
+      </c>
+      <c r="M7" s="112" t="n">
+        <f aca="false">D7/C7</f>
+        <v>0.0590717299578059</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="113" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="137" t="n">
+        <v>3265</v>
+      </c>
+      <c r="C8" s="115" t="n">
+        <v>235</v>
+      </c>
+      <c r="D8" s="115" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="138" t="n">
+        <f aca="false">B8/C8</f>
+        <v>13.8936170212766</v>
+      </c>
+      <c r="F8" s="138" t="n">
+        <f aca="false">B8/D8</f>
+        <v>233.214285714286</v>
+      </c>
+      <c r="G8" s="138" t="n">
+        <f aca="false">D8/C8*100</f>
+        <v>5.95744680851064</v>
+      </c>
+      <c r="H8" s="114" t="n">
+        <v>65500</v>
+      </c>
+      <c r="I8" s="114" t="n">
+        <v>97000</v>
+      </c>
+      <c r="J8" s="139" t="n">
+        <f aca="false">I8/H8</f>
+        <v>1.48091603053435</v>
+      </c>
+      <c r="K8" s="114" t="n">
+        <v>36851919</v>
+      </c>
+      <c r="L8" s="116" t="n">
+        <f aca="false">K8/B8</f>
+        <v>11286.9583460949</v>
+      </c>
+      <c r="M8" s="118" t="n">
+        <f aca="false">D8/C8</f>
+        <v>0.0595744680851064</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="134" t="n">
+        <v>3223</v>
+      </c>
+      <c r="C9" s="109" t="n">
+        <v>230</v>
+      </c>
+      <c r="D9" s="109" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E9" s="135" t="n">
+        <f aca="false">B9/C9</f>
+        <v>14.0130434782609</v>
+      </c>
+      <c r="F9" s="135" t="n">
+        <f aca="false">B9/D9</f>
+        <v>238.740740740741</v>
+      </c>
+      <c r="G9" s="135" t="n">
+        <f aca="false">D9/C9*100</f>
+        <v>5.86956521739131</v>
+      </c>
+      <c r="H9" s="108" t="n">
+        <v>66500</v>
+      </c>
+      <c r="I9" s="108" t="n">
+        <v>98000</v>
+      </c>
+      <c r="J9" s="136" t="n">
+        <f aca="false">I9/H9</f>
+        <v>1.47368421052632</v>
+      </c>
+      <c r="K9" s="108" t="n">
+        <v>36631261</v>
+      </c>
+      <c r="L9" s="110" t="n">
+        <f aca="false">K9/B9</f>
+        <v>11365.5789636984</v>
+      </c>
+      <c r="M9" s="112" t="n">
+        <f aca="false">D9/C9</f>
+        <v>0.058695652173913</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="113" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="137" t="n">
+        <v>3210</v>
+      </c>
+      <c r="C10" s="115" t="n">
+        <v>228</v>
+      </c>
+      <c r="D10" s="115" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E10" s="138" t="n">
+        <f aca="false">B10/C10</f>
+        <v>14.0789473684211</v>
+      </c>
+      <c r="F10" s="138" t="n">
+        <f aca="false">B10/D10</f>
+        <v>237.777777777778</v>
+      </c>
+      <c r="G10" s="138" t="n">
+        <f aca="false">D10/C10*100</f>
+        <v>5.92105263157895</v>
+      </c>
+      <c r="H10" s="114" t="n">
+        <v>67500</v>
+      </c>
+      <c r="I10" s="114" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J10" s="139" t="n">
+        <f aca="false">I10/H10</f>
+        <v>1.48148148148148</v>
+      </c>
+      <c r="K10" s="114" t="n">
+        <v>36829159</v>
+      </c>
+      <c r="L10" s="116" t="n">
+        <f aca="false">K10/B10</f>
+        <v>11473.2582554517</v>
+      </c>
+      <c r="M10" s="118" t="n">
+        <f aca="false">D10/C10</f>
+        <v>0.0592105263157895</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="107" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="134" t="n">
+        <v>3150</v>
+      </c>
+      <c r="C11" s="109" t="n">
+        <v>222</v>
+      </c>
+      <c r="D11" s="109" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" s="135" t="n">
+        <f aca="false">B11/C11</f>
+        <v>14.1891891891892</v>
+      </c>
+      <c r="F11" s="135" t="n">
+        <f aca="false">B11/D11</f>
+        <v>242.307692307692</v>
+      </c>
+      <c r="G11" s="135" t="n">
+        <f aca="false">D11/C11*100</f>
+        <v>5.85585585585586</v>
+      </c>
+      <c r="H11" s="108" t="n">
+        <v>68500</v>
+      </c>
+      <c r="I11" s="108" t="n">
+        <v>102000</v>
+      </c>
+      <c r="J11" s="136" t="n">
+        <f aca="false">I11/H11</f>
+        <v>1.48905109489051</v>
+      </c>
+      <c r="K11" s="108" t="n">
+        <v>37529524</v>
+      </c>
+      <c r="L11" s="110" t="n">
+        <f aca="false">K11/B11</f>
+        <v>11914.1346031746</v>
+      </c>
+      <c r="M11" s="112" t="n">
+        <f aca="false">D11/C11</f>
+        <v>0.0585585585585586</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="113" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="137" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C12" s="115" t="n">
+        <v>218</v>
+      </c>
+      <c r="D12" s="115" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" s="138" t="n">
+        <f aca="false">B12/C12</f>
+        <v>14.2201834862385</v>
+      </c>
+      <c r="F12" s="138" t="n">
+        <f aca="false">B12/D12</f>
+        <v>238.461538461538</v>
+      </c>
+      <c r="G12" s="138" t="n">
+        <f aca="false">D12/C12*100</f>
+        <v>5.96330275229358</v>
+      </c>
+      <c r="H12" s="114" t="n">
+        <v>70000</v>
+      </c>
+      <c r="I12" s="114" t="n">
+        <v>104000</v>
+      </c>
+      <c r="J12" s="139" t="n">
+        <f aca="false">I12/H12</f>
+        <v>1.48571428571429</v>
+      </c>
+      <c r="K12" s="114" t="n">
+        <v>39074698</v>
+      </c>
+      <c r="L12" s="116" t="n">
+        <f aca="false">K12/B12</f>
+        <v>12604.7412903226</v>
+      </c>
+      <c r="M12" s="118" t="n">
+        <f aca="false">D12/C12</f>
+        <v>0.0596330275229358</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="134" t="n">
+        <v>2975</v>
+      </c>
+      <c r="C13" s="109" t="n">
+        <v>213</v>
+      </c>
+      <c r="D13" s="109" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" s="135" t="n">
+        <f aca="false">B13/C13</f>
+        <v>13.9671361502347</v>
+      </c>
+      <c r="F13" s="135" t="n">
+        <f aca="false">B13/D13</f>
+        <v>228.846153846154</v>
+      </c>
+      <c r="G13" s="135" t="n">
+        <f aca="false">D13/C13*100</f>
+        <v>6.10328638497653</v>
+      </c>
+      <c r="H13" s="108" t="n">
+        <v>71500</v>
+      </c>
+      <c r="I13" s="108" t="n">
+        <v>106000</v>
+      </c>
+      <c r="J13" s="136" t="n">
+        <f aca="false">I13/H13</f>
+        <v>1.48251748251748</v>
+      </c>
+      <c r="K13" s="108" t="n">
+        <v>39650662</v>
+      </c>
+      <c r="L13" s="110" t="n">
+        <f aca="false">K13/B13</f>
+        <v>13327.9536134454</v>
+      </c>
+      <c r="M13" s="112" t="n">
+        <f aca="false">D13/C13</f>
+        <v>0.0610328638497653</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="137" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C14" s="115" t="n">
+        <v>208</v>
+      </c>
+      <c r="D14" s="115" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" s="138" t="n">
+        <f aca="false">B14/C14</f>
+        <v>13.7019230769231</v>
+      </c>
+      <c r="F14" s="138" t="n">
+        <f aca="false">B14/D14</f>
+        <v>219.230769230769</v>
+      </c>
+      <c r="G14" s="138" t="n">
+        <f aca="false">D14/C14*100</f>
+        <v>6.25</v>
+      </c>
+      <c r="H14" s="114" t="n">
+        <v>73000</v>
+      </c>
+      <c r="I14" s="114" t="n">
+        <v>108000</v>
+      </c>
+      <c r="J14" s="139" t="n">
+        <f aca="false">I14/H14</f>
+        <v>1.47945205479452</v>
+      </c>
+      <c r="K14" s="114" t="n">
+        <v>39805000</v>
+      </c>
+      <c r="L14" s="116" t="n">
+        <f aca="false">K14/B14</f>
+        <v>13966.6666666667</v>
+      </c>
+      <c r="M14" s="118" t="n">
+        <f aca="false">D14/C14</f>
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="107" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="134" t="n">
+        <v>2727</v>
+      </c>
+      <c r="C15" s="109" t="n">
+        <v>201</v>
+      </c>
+      <c r="D15" s="109" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" s="135" t="n">
+        <f aca="false">B15/C15</f>
+        <v>13.5671641791045</v>
+      </c>
+      <c r="F15" s="135" t="n">
+        <f aca="false">B15/D15</f>
+        <v>209.769230769231</v>
+      </c>
+      <c r="G15" s="135" t="n">
+        <f aca="false">D15/C15*100</f>
+        <v>6.46766169154229</v>
+      </c>
+      <c r="H15" s="108" t="n">
+        <v>74500</v>
+      </c>
+      <c r="I15" s="108" t="n">
+        <v>110000</v>
+      </c>
+      <c r="J15" s="136" t="n">
+        <f aca="false">I15/H15</f>
+        <v>1.47651006711409</v>
+      </c>
+      <c r="K15" s="108" t="n">
+        <v>39704000</v>
+      </c>
+      <c r="L15" s="110" t="n">
+        <f aca="false">K15/B15</f>
+        <v>14559.5892922626</v>
+      </c>
+      <c r="M15" s="112" t="n">
+        <f aca="false">D15/C15</f>
+        <v>0.0646766169154229</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="113" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="137" t="n">
+        <v>2488</v>
+      </c>
+      <c r="C16" s="115" t="n">
+        <v>195</v>
+      </c>
+      <c r="D16" s="115" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E16" s="138" t="n">
+        <f aca="false">B16/C16</f>
+        <v>12.7589743589744</v>
+      </c>
+      <c r="F16" s="138" t="n">
+        <f aca="false">B16/D16</f>
+        <v>184.296296296296</v>
+      </c>
+      <c r="G16" s="138" t="n">
+        <f aca="false">D16/C16*100</f>
+        <v>6.92307692307692</v>
+      </c>
+      <c r="H16" s="114" t="n">
+        <v>76000</v>
+      </c>
+      <c r="I16" s="114" t="n">
+        <v>112000</v>
+      </c>
+      <c r="J16" s="139" t="n">
+        <f aca="false">I16/H16</f>
+        <v>1.47368421052632</v>
+      </c>
+      <c r="K16" s="114" t="n">
+        <v>40633000</v>
+      </c>
+      <c r="L16" s="116" t="n">
+        <f aca="false">K16/B16</f>
+        <v>16331.5916398714</v>
+      </c>
+      <c r="M16" s="118" t="n">
+        <f aca="false">D16/C16</f>
+        <v>0.0692307692307692</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="107" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="134" t="n">
+        <v>2488</v>
+      </c>
+      <c r="C17" s="109" t="n">
+        <v>192</v>
+      </c>
+      <c r="D17" s="109" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E17" s="135" t="n">
+        <f aca="false">B17/C17</f>
+        <v>12.9583333333333</v>
+      </c>
+      <c r="F17" s="135" t="n">
+        <f aca="false">B17/D17</f>
+        <v>184.296296296296</v>
+      </c>
+      <c r="G17" s="135" t="n">
+        <f aca="false">D17/C17*100</f>
+        <v>7.03125</v>
+      </c>
+      <c r="H17" s="108" t="n">
+        <v>78804</v>
+      </c>
+      <c r="I17" s="108" t="n">
+        <v>115000</v>
+      </c>
+      <c r="J17" s="136" t="n">
+        <f aca="false">I17/H17</f>
+        <v>1.45931678594995</v>
+      </c>
+      <c r="K17" s="108" t="n">
+        <v>40542000</v>
+      </c>
+      <c r="L17" s="110" t="n">
+        <f aca="false">K17/B17</f>
+        <v>16295.0160771704</v>
+      </c>
+      <c r="M17" s="112" t="n">
+        <f aca="false">D17/C17</f>
+        <v>0.0703125</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="113" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="137" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C18" s="115" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="D18" s="115" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E18" s="138" t="n">
+        <f aca="false">B18/C18</f>
+        <v>12.9598308668076</v>
+      </c>
+      <c r="F18" s="138" t="n">
+        <f aca="false">B18/D18</f>
+        <v>180.294117647059</v>
+      </c>
+      <c r="G18" s="138" t="n">
+        <f aca="false">D18/C18*100</f>
+        <v>7.18816067653277</v>
+      </c>
+      <c r="H18" s="114" t="n">
+        <v>79500</v>
+      </c>
+      <c r="I18" s="114" t="n">
+        <v>117000</v>
+      </c>
+      <c r="J18" s="139" t="n">
+        <f aca="false">I18/H18</f>
+        <v>1.47169811320755</v>
+      </c>
+      <c r="K18" s="114" t="n">
+        <v>41236000</v>
+      </c>
+      <c r="L18" s="116" t="n">
+        <f aca="false">K18/B18</f>
+        <v>16817.2920065253</v>
+      </c>
+      <c r="M18" s="118" t="n">
+        <f aca="false">D18/C18</f>
+        <v>0.0718816067653277</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="107" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="134" t="n">
+        <v>2321</v>
+      </c>
+      <c r="C19" s="109" t="n">
+        <v>190</v>
+      </c>
+      <c r="D19" s="109" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E19" s="135" t="n">
+        <f aca="false">B19/C19</f>
+        <v>12.2157894736842</v>
+      </c>
+      <c r="F19" s="135" t="n">
+        <f aca="false">B19/D19</f>
+        <v>171.925925925926</v>
+      </c>
+      <c r="G19" s="135" t="n">
+        <f aca="false">D19/C19*100</f>
+        <v>7.10526315789474</v>
+      </c>
+      <c r="H19" s="108" t="n">
+        <v>80500</v>
+      </c>
+      <c r="I19" s="108" t="n">
+        <v>119000</v>
+      </c>
+      <c r="J19" s="136" t="n">
+        <f aca="false">I19/H19</f>
+        <v>1.47826086956522</v>
+      </c>
+      <c r="K19" s="108" t="n">
+        <v>41310000</v>
+      </c>
+      <c r="L19" s="110" t="n">
+        <f aca="false">K19/B19</f>
+        <v>17798.3627746661</v>
+      </c>
+      <c r="M19" s="112" t="n">
+        <f aca="false">D19/C19</f>
+        <v>0.0710526315789474</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="113" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="137" t="n">
+        <v>2321</v>
+      </c>
+      <c r="C20" s="115" t="n">
+        <v>192</v>
+      </c>
+      <c r="D20" s="115" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E20" s="138" t="n">
+        <f aca="false">B20/C20</f>
+        <v>12.0885416666667</v>
+      </c>
+      <c r="F20" s="138" t="n">
+        <f aca="false">B20/D20</f>
+        <v>173.208955223881</v>
+      </c>
+      <c r="G20" s="138" t="n">
+        <f aca="false">D20/C20*100</f>
+        <v>6.97916666666667</v>
+      </c>
+      <c r="H20" s="114" t="n">
+        <v>81500</v>
+      </c>
+      <c r="I20" s="114" t="n">
+        <v>122000</v>
+      </c>
+      <c r="J20" s="139" t="n">
+        <f aca="false">I20/H20</f>
+        <v>1.49693251533742</v>
+      </c>
+      <c r="K20" s="114" t="n">
+        <v>42013000</v>
+      </c>
+      <c r="L20" s="116" t="n">
+        <f aca="false">K20/B20</f>
+        <v>18101.249461439</v>
+      </c>
+      <c r="M20" s="118" t="n">
+        <f aca="false">D20/C20</f>
+        <v>0.0697916666666667</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="107" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="134" t="n">
+        <v>2235</v>
+      </c>
+      <c r="C21" s="109" t="n">
+        <v>195</v>
+      </c>
+      <c r="D21" s="109" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E21" s="135" t="n">
+        <f aca="false">B21/C21</f>
+        <v>11.4615384615385</v>
+      </c>
+      <c r="F21" s="135" t="n">
+        <f aca="false">B21/D21</f>
+        <v>169.318181818182</v>
+      </c>
+      <c r="G21" s="135" t="n">
+        <f aca="false">D21/C21*100</f>
+        <v>6.76923076923077</v>
+      </c>
+      <c r="H21" s="108" t="n">
+        <v>82554</v>
+      </c>
+      <c r="I21" s="108" t="n">
+        <v>125000</v>
+      </c>
+      <c r="J21" s="136" t="n">
+        <f aca="false">I21/H21</f>
+        <v>1.5141604283257</v>
+      </c>
+      <c r="K21" s="108" t="n">
+        <v>43165000</v>
+      </c>
+      <c r="L21" s="110" t="n">
+        <f aca="false">K21/B21</f>
+        <v>19313.1991051454</v>
+      </c>
+      <c r="M21" s="112" t="n">
+        <f aca="false">D21/C21</f>
+        <v>0.0676923076923077</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="137" t="n">
+        <v>2161</v>
+      </c>
+      <c r="C22" s="115" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="D22" s="115" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" s="138" t="n">
+        <f aca="false">B22/C22</f>
+        <v>11.1737331954498</v>
+      </c>
+      <c r="F22" s="138" t="n">
+        <f aca="false">B22/D22</f>
+        <v>166.230769230769</v>
+      </c>
+      <c r="G22" s="138" t="n">
+        <f aca="false">D22/C22*100</f>
+        <v>6.72182006204757</v>
+      </c>
+      <c r="H22" s="114" t="n">
+        <v>84000</v>
+      </c>
+      <c r="I22" s="114" t="n">
+        <v>128000</v>
+      </c>
+      <c r="J22" s="139" t="n">
+        <f aca="false">I22/H22</f>
+        <v>1.52380952380952</v>
+      </c>
+      <c r="K22" s="114" t="n">
+        <v>43979351</v>
+      </c>
+      <c r="L22" s="116" t="n">
+        <f aca="false">K22/B22</f>
+        <v>20351.3887089311</v>
+      </c>
+      <c r="M22" s="118" t="n">
+        <f aca="false">D22/C22</f>
+        <v>0.0672182006204757</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="107" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="134" t="n">
+        <v>2235</v>
+      </c>
+      <c r="C23" s="109" t="n">
+        <v>191.4</v>
+      </c>
+      <c r="D23" s="109" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E23" s="135" t="n">
+        <f aca="false">B23/C23</f>
+        <v>11.6771159874608</v>
+      </c>
+      <c r="F23" s="135" t="n">
+        <f aca="false">B23/D23</f>
+        <v>174.609375</v>
+      </c>
+      <c r="G23" s="135" t="n">
+        <f aca="false">D23/C23*100</f>
+        <v>6.68756530825496</v>
+      </c>
+      <c r="H23" s="108" t="n">
+        <v>85500</v>
+      </c>
+      <c r="I23" s="108" t="n">
+        <v>131000</v>
+      </c>
+      <c r="J23" s="136" t="n">
+        <f aca="false">I23/H23</f>
+        <v>1.53216374269006</v>
+      </c>
+      <c r="K23" s="108" t="n">
+        <v>45576075</v>
+      </c>
+      <c r="L23" s="110" t="n">
+        <f aca="false">K23/B23</f>
+        <v>20391.9798657718</v>
+      </c>
+      <c r="M23" s="112" t="n">
+        <f aca="false">D23/C23</f>
+        <v>0.0668756530825496</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="105" t="s">
+        <v>235</v>
+      </c>
+      <c r="B25" s="105"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="105"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="119" t="s">
+        <v>275</v>
+      </c>
+      <c r="B26" s="112" t="n">
+        <f aca="false">(B23-B7)/B7</f>
+        <v>-0.315886134067952</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="119" t="s">
+        <v>276</v>
+      </c>
+      <c r="B27" s="112" t="n">
+        <f aca="false">(C23-C7)/C7</f>
+        <v>-0.192405063291139</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="119" t="s">
+        <v>277</v>
+      </c>
+      <c r="B28" s="112" t="n">
+        <f aca="false">(D23-D7)/D7</f>
+        <v>-0.0857142857142857</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="119" t="s">
+        <v>278</v>
+      </c>
+      <c r="B29" s="112" t="n">
+        <f aca="false">(H23-H7)/H7</f>
+        <v>0.325581395348837</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="119" t="s">
+        <v>279</v>
+      </c>
+      <c r="B30" s="112" t="n">
+        <f aca="false">(I23-I7)/I7</f>
+        <v>0.378947368421053</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="119" t="s">
+        <v>280</v>
+      </c>
+      <c r="B31" s="112" t="n">
+        <f aca="false">(L23-L7)/L7</f>
+        <v>0.834465767212199</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="119" t="s">
+        <v>281</v>
+      </c>
+      <c r="B32" s="135" t="n">
+        <f aca="false">E7</f>
+        <v>13.7848101265823</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="119" t="s">
+        <v>282</v>
+      </c>
+      <c r="B33" s="135" t="n">
+        <f aca="false">E23</f>
+        <v>11.6771159874608</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="119" t="s">
+        <v>283</v>
+      </c>
+      <c r="B34" s="135" t="n">
+        <f aca="false">F7</f>
+        <v>233.357142857143</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="119" t="s">
+        <v>284</v>
+      </c>
+      <c r="B35" s="135" t="n">
+        <f aca="false">F23</f>
+        <v>174.609375</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="119" t="s">
+        <v>285</v>
+      </c>
+      <c r="B36" s="135" t="n">
+        <f aca="false">G7</f>
+        <v>5.90717299578059</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="119" t="s">
+        <v>286</v>
+      </c>
+      <c r="B37" s="135" t="n">
+        <f aca="false">G23</f>
+        <v>6.68756530825496</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="119" t="s">
+        <v>287</v>
+      </c>
+      <c r="B38" s="110" t="n">
+        <f aca="false">L7</f>
+        <v>11116.0318334864</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="119" t="s">
+        <v>288</v>
+      </c>
+      <c r="B39" s="110" t="n">
+        <f aca="false">L23</f>
+        <v>20391.9798657718</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="105" t="s">
+        <v>289</v>
+      </c>
+      <c r="B41" s="105"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="105"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="140" t="s">
+        <v>290</v>
+      </c>
+      <c r="B42" s="140" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="140" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="140" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="140" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="107" t="s">
+        <v>291</v>
+      </c>
+      <c r="B43" s="141" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="C43" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="141" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="E43" s="141" t="n">
+        <v>163.4</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="143" t="s">
+        <v>292</v>
+      </c>
+      <c r="B44" s="144" t="n">
+        <v>28</v>
+      </c>
+      <c r="C44" s="145" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="145" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="144" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="107" t="s">
+        <v>293</v>
+      </c>
+      <c r="B45" s="141" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="C45" s="141" t="n">
+        <v>195</v>
+      </c>
+      <c r="D45" s="141" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="E45" s="141" t="n">
+        <v>191.4</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="143" t="s">
+        <v>294</v>
+      </c>
+      <c r="B46" s="144" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="C46" s="145" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="145" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="144" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="107" t="s">
+        <v>295</v>
+      </c>
+      <c r="B47" s="146" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="C47" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="146" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="143" t="s">
+        <v>296</v>
+      </c>
+      <c r="B48" s="144" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" s="144" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D48" s="144" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E48" s="144" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="107" t="s">
+        <v>297</v>
+      </c>
+      <c r="B49" s="146" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C49" s="146" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="D49" s="146" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="E49" s="146" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="143" t="s">
+        <v>298</v>
+      </c>
+      <c r="B50" s="144" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="C50" s="144" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D50" s="144" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E50" s="144" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="107" t="s">
+        <v>299</v>
+      </c>
+      <c r="B51" s="146" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C51" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="146" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="143" t="s">
+        <v>300</v>
+      </c>
+      <c r="B52" s="144" t="n">
+        <v>17</v>
+      </c>
+      <c r="C52" s="145" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="145" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="144" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="107" t="s">
+        <v>301</v>
+      </c>
+      <c r="B53" s="146" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C53" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="146" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="143" t="s">
+        <v>302</v>
+      </c>
+      <c r="B54" s="144" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" s="145" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="145" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="144" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="107" t="s">
+        <v>303</v>
+      </c>
+      <c r="B55" s="141" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="C55" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="141" t="n">
+        <v>102.3</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="143" t="s">
+        <v>304</v>
+      </c>
+      <c r="B56" s="147" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C56" s="147" t="n">
+        <v>2235</v>
+      </c>
+      <c r="D56" s="147" t="n">
+        <v>2161</v>
+      </c>
+      <c r="E56" s="147" t="n">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="107" t="s">
+        <v>305</v>
+      </c>
+      <c r="B57" s="146" t="n">
+        <v>13</v>
+      </c>
+      <c r="C57" s="146" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D57" s="146" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E57" s="146" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="81" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="38" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="38" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="38" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="38" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="38" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="38" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="38" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="38" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="38" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="148" t="s">
+        <v>317</v>
+      </c>
+      <c r="B72" s="148"/>
+      <c r="C72" s="148"/>
+      <c r="D72" s="148"/>
+      <c r="E72" s="148"/>
+      <c r="F72" s="148"/>
+      <c r="G72" s="148"/>
+      <c r="H72" s="148"/>
+      <c r="I72" s="148"/>
+      <c r="J72" s="148"/>
+      <c r="K72" s="148"/>
+      <c r="L72" s="148"/>
+      <c r="M72" s="148"/>
+      <c r="N72" s="131"/>
+    </row>
+    <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="149" t="s">
+        <v>1</v>
+      </c>
+      <c r="B73" s="149" t="s">
+        <v>318</v>
+      </c>
+      <c r="C73" s="149" t="s">
+        <v>319</v>
+      </c>
+      <c r="D73" s="149" t="s">
+        <v>320</v>
+      </c>
+      <c r="E73" s="149" t="s">
+        <v>321</v>
+      </c>
+      <c r="F73" s="149" t="s">
+        <v>322</v>
+      </c>
+      <c r="G73" s="149" t="s">
+        <v>323</v>
+      </c>
+      <c r="H73" s="149" t="s">
+        <v>324</v>
+      </c>
+      <c r="I73" s="149" t="s">
+        <v>325</v>
+      </c>
+      <c r="J73" s="149" t="s">
+        <v>326</v>
+      </c>
+      <c r="K73" s="149" t="s">
+        <v>327</v>
+      </c>
+      <c r="L73" s="149" t="s">
+        <v>328</v>
+      </c>
+      <c r="M73" s="149" t="s">
+        <v>329</v>
+      </c>
+      <c r="N73" s="131"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B74" s="150" t="n">
+        <v>3267</v>
+      </c>
+      <c r="C74" s="151" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="D74" s="151" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E74" s="152" t="n">
+        <f aca="false">C74+D74</f>
+        <v>231.6</v>
+      </c>
+      <c r="F74" s="151" t="n">
+        <v>10</v>
+      </c>
+      <c r="G74" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" s="154" t="n">
+        <f aca="false">F74+G74</f>
+        <v>14</v>
+      </c>
+      <c r="I74" s="151" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J74" s="154" t="n">
+        <f aca="false">H74+I74</f>
+        <v>28.6</v>
+      </c>
+      <c r="K74" s="154" t="n">
+        <f aca="false">B74/E74</f>
+        <v>14.1062176165803</v>
+      </c>
+      <c r="L74" s="154" t="n">
+        <f aca="false">B74/H74</f>
+        <v>233.357142857143</v>
+      </c>
+      <c r="M74" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N74" s="131"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B75" s="150" t="n">
+        <v>3265</v>
+      </c>
+      <c r="C75" s="151" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="D75" s="151" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E75" s="152" t="n">
+        <f aca="false">C75+D75</f>
+        <v>228.3</v>
+      </c>
+      <c r="F75" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G75" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" s="154" t="n">
+        <f aca="false">F75+G75</f>
+        <v>13</v>
+      </c>
+      <c r="I75" s="151" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J75" s="154" t="n">
+        <f aca="false">H75+I75</f>
+        <v>27.8</v>
+      </c>
+      <c r="K75" s="154" t="n">
+        <f aca="false">B75/E75</f>
+        <v>14.3013578624617</v>
+      </c>
+      <c r="L75" s="154" t="n">
+        <f aca="false">B75/H75</f>
+        <v>251.153846153846</v>
+      </c>
+      <c r="M75" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N75" s="131"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B76" s="150" t="n">
+        <v>3223</v>
+      </c>
+      <c r="C76" s="151" t="n">
+        <v>194.3</v>
+      </c>
+      <c r="D76" s="151" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E76" s="152" t="n">
+        <f aca="false">C76+D76</f>
+        <v>220.8</v>
+      </c>
+      <c r="F76" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G76" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="154" t="n">
+        <f aca="false">F76+G76</f>
+        <v>13</v>
+      </c>
+      <c r="I76" s="151" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J76" s="154" t="n">
+        <f aca="false">H76+I76</f>
+        <v>26.1</v>
+      </c>
+      <c r="K76" s="154" t="n">
+        <f aca="false">B76/E76</f>
+        <v>14.5969202898551</v>
+      </c>
+      <c r="L76" s="154" t="n">
+        <f aca="false">B76/H76</f>
+        <v>247.923076923077</v>
+      </c>
+      <c r="M76" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N76" s="131"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="150" t="n">
+        <v>3210</v>
+      </c>
+      <c r="C77" s="151" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="D77" s="151" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E77" s="152" t="n">
+        <f aca="false">C77+D77</f>
+        <v>213</v>
+      </c>
+      <c r="F77" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G77" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H77" s="154" t="n">
+        <f aca="false">F77+G77</f>
+        <v>13</v>
+      </c>
+      <c r="I77" s="151" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J77" s="154" t="n">
+        <f aca="false">H77+I77</f>
+        <v>27.4</v>
+      </c>
+      <c r="K77" s="154" t="n">
+        <f aca="false">B77/E77</f>
+        <v>15.0704225352113</v>
+      </c>
+      <c r="L77" s="154" t="n">
+        <f aca="false">B77/H77</f>
+        <v>246.923076923077</v>
+      </c>
+      <c r="M77" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N77" s="131"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B78" s="150" t="n">
+        <v>3150</v>
+      </c>
+      <c r="C78" s="151" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="D78" s="151" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E78" s="152" t="n">
+        <f aca="false">C78+D78</f>
+        <v>205.7</v>
+      </c>
+      <c r="F78" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G78" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="154" t="n">
+        <f aca="false">F78+G78</f>
+        <v>13</v>
+      </c>
+      <c r="I78" s="151" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J78" s="154" t="n">
+        <f aca="false">H78+I78</f>
+        <v>27.2</v>
+      </c>
+      <c r="K78" s="154" t="n">
+        <f aca="false">B78/E78</f>
+        <v>15.3135634419057</v>
+      </c>
+      <c r="L78" s="154" t="n">
+        <f aca="false">B78/H78</f>
+        <v>242.307692307692</v>
+      </c>
+      <c r="M78" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N78" s="131"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" s="150" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C79" s="151" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="D79" s="151" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E79" s="152" t="n">
+        <f aca="false">C79+D79</f>
+        <v>207.1</v>
+      </c>
+      <c r="F79" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G79" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H79" s="154" t="n">
+        <f aca="false">F79+G79</f>
+        <v>13</v>
+      </c>
+      <c r="I79" s="151" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J79" s="154" t="n">
+        <f aca="false">H79+I79</f>
+        <v>24.6</v>
+      </c>
+      <c r="K79" s="154" t="n">
+        <f aca="false">B79/E79</f>
+        <v>14.9686141960406</v>
+      </c>
+      <c r="L79" s="154" t="n">
+        <f aca="false">B79/H79</f>
+        <v>238.461538461538</v>
+      </c>
+      <c r="M79" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N79" s="131"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="B80" s="150" t="n">
+        <v>2975</v>
+      </c>
+      <c r="C80" s="151" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="D80" s="151" t="n">
+        <v>23</v>
+      </c>
+      <c r="E80" s="152" t="n">
+        <f aca="false">C80+D80</f>
+        <v>198.8</v>
+      </c>
+      <c r="F80" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G80" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H80" s="154" t="n">
+        <f aca="false">F80+G80</f>
+        <v>13</v>
+      </c>
+      <c r="I80" s="151" t="n">
+        <v>12</v>
+      </c>
+      <c r="J80" s="154" t="n">
+        <f aca="false">H80+I80</f>
+        <v>25</v>
+      </c>
+      <c r="K80" s="154" t="n">
+        <f aca="false">B80/E80</f>
+        <v>14.9647887323944</v>
+      </c>
+      <c r="L80" s="154" t="n">
+        <f aca="false">B80/H80</f>
+        <v>228.846153846154</v>
+      </c>
+      <c r="M80" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N80" s="131"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="B81" s="150" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C81" s="151" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="D81" s="151" t="n">
+        <v>24</v>
+      </c>
+      <c r="E81" s="152" t="n">
+        <f aca="false">C81+D81</f>
+        <v>195.2</v>
+      </c>
+      <c r="F81" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G81" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" s="154" t="n">
+        <f aca="false">F81+G81</f>
+        <v>13</v>
+      </c>
+      <c r="I81" s="151" t="n">
+        <v>14</v>
+      </c>
+      <c r="J81" s="154" t="n">
+        <f aca="false">H81+I81</f>
+        <v>27</v>
+      </c>
+      <c r="K81" s="154" t="n">
+        <f aca="false">B81/E81</f>
+        <v>14.6004098360656</v>
+      </c>
+      <c r="L81" s="154" t="n">
+        <f aca="false">B81/H81</f>
+        <v>219.230769230769</v>
+      </c>
+      <c r="M81" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N81" s="131"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B82" s="150" t="n">
+        <v>2727</v>
+      </c>
+      <c r="C82" s="151" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="D82" s="151" t="n">
+        <v>24</v>
+      </c>
+      <c r="E82" s="152" t="n">
+        <f aca="false">C82+D82</f>
+        <v>190.3</v>
+      </c>
+      <c r="F82" s="151" t="n">
+        <v>10</v>
+      </c>
+      <c r="G82" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" s="154" t="n">
+        <f aca="false">F82+G82</f>
+        <v>14</v>
+      </c>
+      <c r="I82" s="151" t="n">
+        <v>13</v>
+      </c>
+      <c r="J82" s="154" t="n">
+        <f aca="false">H82+I82</f>
+        <v>27</v>
+      </c>
+      <c r="K82" s="154" t="n">
+        <f aca="false">B82/E82</f>
+        <v>14.3300052548607</v>
+      </c>
+      <c r="L82" s="154" t="n">
+        <f aca="false">B82/H82</f>
+        <v>194.785714285714</v>
+      </c>
+      <c r="M82" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N82" s="131"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" s="150" t="n">
+        <v>2488</v>
+      </c>
+      <c r="C83" s="151" t="n">
+        <v>160.4</v>
+      </c>
+      <c r="D83" s="151" t="n">
+        <v>24</v>
+      </c>
+      <c r="E83" s="152" t="n">
+        <f aca="false">C83+D83</f>
+        <v>184.4</v>
+      </c>
+      <c r="F83" s="151" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="G83" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H83" s="154" t="n">
+        <f aca="false">F83+G83</f>
+        <v>13.8</v>
+      </c>
+      <c r="I83" s="151" t="n">
+        <v>14</v>
+      </c>
+      <c r="J83" s="154" t="n">
+        <f aca="false">H83+I83</f>
+        <v>27.8</v>
+      </c>
+      <c r="K83" s="154" t="n">
+        <f aca="false">B83/E83</f>
+        <v>13.4924078091106</v>
+      </c>
+      <c r="L83" s="154" t="n">
+        <f aca="false">B83/H83</f>
+        <v>180.289855072464</v>
+      </c>
+      <c r="M83" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N83" s="131"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B84" s="150" t="n">
+        <v>2488</v>
+      </c>
+      <c r="C84" s="151" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="D84" s="151" t="n">
+        <v>27</v>
+      </c>
+      <c r="E84" s="152" t="n">
+        <f aca="false">C84+D84</f>
+        <v>188.7</v>
+      </c>
+      <c r="F84" s="151" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G84" s="153" t="n">
+        <v>4</v>
+      </c>
+      <c r="H84" s="154" t="n">
+        <f aca="false">F84+G84</f>
+        <v>13.6</v>
+      </c>
+      <c r="I84" s="151" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J84" s="154" t="n">
+        <f aca="false">H84+I84</f>
+        <v>27</v>
+      </c>
+      <c r="K84" s="154" t="n">
+        <f aca="false">B84/E84</f>
+        <v>13.1849496555379</v>
+      </c>
+      <c r="L84" s="154" t="n">
+        <f aca="false">B84/H84</f>
+        <v>182.941176470588</v>
+      </c>
+      <c r="M84" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N84" s="131"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B85" s="150" t="n">
+        <v>2452</v>
+      </c>
+      <c r="C85" s="151" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="D85" s="151" t="n">
+        <v>26</v>
+      </c>
+      <c r="E85" s="152" t="n">
+        <f aca="false">C85+D85</f>
+        <v>187.3</v>
+      </c>
+      <c r="F85" s="151" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G85" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="H85" s="154" t="n">
+        <f aca="false">F85+G85</f>
+        <v>13.6</v>
+      </c>
+      <c r="I85" s="151" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J85" s="154" t="n">
+        <f aca="false">H85+I85</f>
+        <v>25.2</v>
+      </c>
+      <c r="K85" s="154" t="n">
+        <f aca="false">B85/E85</f>
+        <v>13.0912973838761</v>
+      </c>
+      <c r="L85" s="154" t="n">
+        <f aca="false">B85/H85</f>
+        <v>180.294117647059</v>
+      </c>
+      <c r="M85" s="156" t="s">
+        <v>331</v>
+      </c>
+      <c r="N85" s="131"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="B86" s="150" t="n">
+        <v>2321</v>
+      </c>
+      <c r="C86" s="151" t="n">
+        <v>160.8</v>
+      </c>
+      <c r="D86" s="151" t="n">
+        <v>26</v>
+      </c>
+      <c r="E86" s="152" t="n">
+        <f aca="false">C86+D86</f>
+        <v>186.8</v>
+      </c>
+      <c r="F86" s="151" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G86" s="153" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H86" s="154" t="n">
+        <f aca="false">F86+G86</f>
+        <v>13.1</v>
+      </c>
+      <c r="I86" s="151" t="n">
+        <v>13</v>
+      </c>
+      <c r="J86" s="154" t="n">
+        <f aca="false">H86+I86</f>
+        <v>26.1</v>
+      </c>
+      <c r="K86" s="154" t="n">
+        <f aca="false">B86/E86</f>
+        <v>12.4250535331906</v>
+      </c>
+      <c r="L86" s="154" t="n">
+        <f aca="false">B86/H86</f>
+        <v>177.175572519084</v>
+      </c>
+      <c r="M86" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N86" s="131"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="B87" s="150" t="n">
+        <v>2321</v>
+      </c>
+      <c r="C87" s="151" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="D87" s="151" t="n">
+        <v>25</v>
+      </c>
+      <c r="E87" s="152" t="n">
+        <f aca="false">C87+D87</f>
+        <v>186.4</v>
+      </c>
+      <c r="F87" s="151" t="n">
+        <v>9.7</v>
+      </c>
+      <c r="G87" s="153" t="n">
+        <v>3</v>
+      </c>
+      <c r="H87" s="154" t="n">
+        <f aca="false">F87+G87</f>
+        <v>12.7</v>
+      </c>
+      <c r="I87" s="151" t="n">
+        <v>14</v>
+      </c>
+      <c r="J87" s="154" t="n">
+        <f aca="false">H87+I87</f>
+        <v>26.7</v>
+      </c>
+      <c r="K87" s="154" t="n">
+        <f aca="false">B87/E87</f>
+        <v>12.4517167381974</v>
+      </c>
+      <c r="L87" s="154" t="n">
+        <f aca="false">B87/H87</f>
+        <v>182.755905511811</v>
+      </c>
+      <c r="M87" s="155" t="s">
+        <v>330</v>
+      </c>
+      <c r="N87" s="131"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="B88" s="150" t="n">
+        <v>2235</v>
+      </c>
+      <c r="C88" s="151" t="n">
+        <v>161</v>
+      </c>
+      <c r="D88" s="151" t="n">
+        <v>26</v>
+      </c>
+      <c r="E88" s="152" t="n">
+        <f aca="false">C88+D88</f>
+        <v>187</v>
+      </c>
+      <c r="F88" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G88" s="151" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H88" s="154" t="n">
+        <f aca="false">F88+G88</f>
+        <v>11.8</v>
+      </c>
+      <c r="I88" s="151" t="n">
+        <v>15</v>
+      </c>
+      <c r="J88" s="154" t="n">
+        <f aca="false">H88+I88</f>
+        <v>26.8</v>
+      </c>
+      <c r="K88" s="154" t="n">
+        <f aca="false">B88/E88</f>
+        <v>11.951871657754</v>
+      </c>
+      <c r="L88" s="154" t="n">
+        <f aca="false">B88/H88</f>
+        <v>189.406779661017</v>
+      </c>
+      <c r="M88" s="156" t="s">
+        <v>331</v>
+      </c>
+      <c r="N88" s="131"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="B89" s="150" t="n">
+        <v>2161</v>
+      </c>
+      <c r="C89" s="151" t="n">
+        <v>162.4</v>
+      </c>
+      <c r="D89" s="151" t="n">
+        <v>24</v>
+      </c>
+      <c r="E89" s="152" t="n">
+        <f aca="false">C89+D89</f>
+        <v>186.4</v>
+      </c>
+      <c r="F89" s="151" t="n">
+        <v>10</v>
+      </c>
+      <c r="G89" s="151" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H89" s="154" t="n">
+        <f aca="false">F89+G89</f>
+        <v>12.8</v>
+      </c>
+      <c r="I89" s="151" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J89" s="154" t="n">
+        <f aca="false">H89+I89</f>
+        <v>29.4</v>
+      </c>
+      <c r="K89" s="154" t="n">
+        <f aca="false">B89/E89</f>
+        <v>11.593347639485</v>
+      </c>
+      <c r="L89" s="154" t="n">
+        <f aca="false">B89/H89</f>
+        <v>168.828125</v>
+      </c>
+      <c r="M89" s="156" t="s">
+        <v>331</v>
+      </c>
+      <c r="N89" s="131"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B90" s="150" t="n">
+        <v>2235</v>
+      </c>
+      <c r="C90" s="151" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="D90" s="151" t="n">
+        <v>28</v>
+      </c>
+      <c r="E90" s="152" t="n">
+        <f aca="false">C90+D90</f>
+        <v>189.5</v>
+      </c>
+      <c r="F90" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="G90" s="151" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H90" s="154" t="n">
+        <f aca="false">F90+G90</f>
+        <v>11.8</v>
+      </c>
+      <c r="I90" s="151" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J90" s="154" t="n">
+        <f aca="false">H90+I90</f>
+        <v>28.5</v>
+      </c>
+      <c r="K90" s="154" t="n">
+        <f aca="false">B90/E90</f>
+        <v>11.7941952506596</v>
+      </c>
+      <c r="L90" s="154" t="n">
+        <f aca="false">B90/H90</f>
+        <v>189.406779661017</v>
+      </c>
+      <c r="M90" s="156" t="s">
+        <v>331</v>
+      </c>
+      <c r="N90" s="131"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="131"/>
+      <c r="B91" s="131"/>
+      <c r="C91" s="131"/>
+      <c r="D91" s="131"/>
+      <c r="E91" s="131"/>
+      <c r="F91" s="131"/>
+      <c r="G91" s="131"/>
+      <c r="H91" s="131"/>
+      <c r="I91" s="131"/>
+      <c r="J91" s="131"/>
+      <c r="K91" s="131"/>
+      <c r="L91" s="131"/>
+      <c r="M91" s="131"/>
+      <c r="N91" s="131"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="B92" s="27" t="n">
+        <f aca="false">(B90-B74)/B74</f>
+        <v>-0.315886134067952</v>
+      </c>
+      <c r="C92" s="157"/>
+      <c r="D92" s="157"/>
+      <c r="E92" s="27" t="n">
+        <f aca="false">(E90-E74)/E74</f>
+        <v>-0.181778929188256</v>
+      </c>
+      <c r="F92" s="27" t="n">
+        <f aca="false">(F90-F74)/F74</f>
+        <v>-0.1</v>
+      </c>
+      <c r="G92" s="157"/>
+      <c r="H92" s="27" t="n">
+        <f aca="false">(H90-H74)/H74</f>
+        <v>-0.157142857142857</v>
+      </c>
+      <c r="I92" s="27" t="n">
+        <f aca="false">(I90-I74)/I74</f>
+        <v>0.143835616438356</v>
+      </c>
+      <c r="J92" s="27" t="n">
+        <f aca="false">(J90-J74)/J74</f>
+        <v>-0.00349650349650355</v>
+      </c>
+      <c r="K92" s="131"/>
+      <c r="L92" s="131"/>
+      <c r="M92" s="131"/>
+      <c r="N92" s="131"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="131"/>
+      <c r="B93" s="131"/>
+      <c r="C93" s="131"/>
+      <c r="D93" s="131"/>
+      <c r="E93" s="131"/>
+      <c r="F93" s="131"/>
+      <c r="G93" s="131"/>
+      <c r="H93" s="131"/>
+      <c r="I93" s="131"/>
+      <c r="J93" s="131"/>
+      <c r="K93" s="131"/>
+      <c r="L93" s="131"/>
+      <c r="M93" s="131"/>
+      <c r="N93" s="131"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="81" t="s">
+        <v>333</v>
+      </c>
+      <c r="B94" s="131"/>
+      <c r="C94" s="131"/>
+      <c r="D94" s="131"/>
+      <c r="E94" s="131"/>
+      <c r="F94" s="131"/>
+      <c r="G94" s="131"/>
+      <c r="H94" s="131"/>
+      <c r="I94" s="131"/>
+      <c r="J94" s="131"/>
+      <c r="K94" s="131"/>
+      <c r="L94" s="131"/>
+      <c r="M94" s="131"/>
+      <c r="N94" s="131"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="158" t="s">
+        <v>334</v>
+      </c>
+      <c r="B95" s="131"/>
+      <c r="C95" s="131"/>
+      <c r="D95" s="131"/>
+      <c r="E95" s="131"/>
+      <c r="F95" s="131"/>
+      <c r="G95" s="131"/>
+      <c r="H95" s="131"/>
+      <c r="I95" s="131"/>
+      <c r="J95" s="131"/>
+      <c r="K95" s="131"/>
+      <c r="L95" s="131"/>
+      <c r="M95" s="131"/>
+      <c r="N95" s="131"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="158" t="s">
+        <v>335</v>
+      </c>
+      <c r="B96" s="131"/>
+      <c r="C96" s="131"/>
+      <c r="D96" s="131"/>
+      <c r="E96" s="131"/>
+      <c r="F96" s="131"/>
+      <c r="G96" s="131"/>
+      <c r="H96" s="131"/>
+      <c r="I96" s="131"/>
+      <c r="J96" s="131"/>
+      <c r="K96" s="131"/>
+      <c r="L96" s="131"/>
+      <c r="M96" s="131"/>
+      <c r="N96" s="131"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="158" t="s">
+        <v>336</v>
+      </c>
+      <c r="B97" s="131"/>
+      <c r="C97" s="131"/>
+      <c r="D97" s="131"/>
+      <c r="E97" s="131"/>
+      <c r="F97" s="131"/>
+      <c r="G97" s="131"/>
+      <c r="H97" s="131"/>
+      <c r="I97" s="131"/>
+      <c r="J97" s="131"/>
+      <c r="K97" s="131"/>
+      <c r="L97" s="131"/>
+      <c r="M97" s="131"/>
+      <c r="N97" s="131"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="158"/>
+      <c r="B98" s="131"/>
+      <c r="C98" s="131"/>
+      <c r="D98" s="131"/>
+      <c r="E98" s="131"/>
+      <c r="F98" s="131"/>
+      <c r="G98" s="131"/>
+      <c r="H98" s="131"/>
+      <c r="I98" s="131"/>
+      <c r="J98" s="131"/>
+      <c r="K98" s="131"/>
+      <c r="L98" s="131"/>
+      <c r="M98" s="131"/>
+      <c r="N98" s="131"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="158" t="s">
+        <v>337</v>
+      </c>
+      <c r="B99" s="131"/>
+      <c r="C99" s="131"/>
+      <c r="D99" s="131"/>
+      <c r="E99" s="131"/>
+      <c r="F99" s="131"/>
+      <c r="G99" s="131"/>
+      <c r="H99" s="131"/>
+      <c r="I99" s="131"/>
+      <c r="J99" s="131"/>
+      <c r="K99" s="131"/>
+      <c r="L99" s="131"/>
+      <c r="M99" s="131"/>
+      <c r="N99" s="131"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="158" t="s">
+        <v>338</v>
+      </c>
+      <c r="B100" s="131"/>
+      <c r="C100" s="131"/>
+      <c r="D100" s="131"/>
+      <c r="E100" s="131"/>
+      <c r="F100" s="131"/>
+      <c r="G100" s="131"/>
+      <c r="H100" s="131"/>
+      <c r="I100" s="131"/>
+      <c r="J100" s="131"/>
+      <c r="K100" s="131"/>
+      <c r="L100" s="131"/>
+      <c r="M100" s="131"/>
+      <c r="N100" s="131"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="158" t="s">
+        <v>339</v>
+      </c>
+      <c r="B101" s="131"/>
+      <c r="C101" s="131"/>
+      <c r="D101" s="131"/>
+      <c r="E101" s="131"/>
+      <c r="F101" s="131"/>
+      <c r="G101" s="131"/>
+      <c r="H101" s="131"/>
+      <c r="I101" s="131"/>
+      <c r="J101" s="131"/>
+      <c r="K101" s="131"/>
+      <c r="L101" s="131"/>
+      <c r="M101" s="131"/>
+      <c r="N101" s="131"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="131"/>
+      <c r="B102" s="131"/>
+      <c r="C102" s="131"/>
+      <c r="D102" s="131"/>
+      <c r="E102" s="131"/>
+      <c r="F102" s="131"/>
+      <c r="G102" s="131"/>
+      <c r="H102" s="131"/>
+      <c r="I102" s="131"/>
+      <c r="J102" s="131"/>
+      <c r="K102" s="131"/>
+      <c r="L102" s="131"/>
+      <c r="M102" s="131"/>
+      <c r="N102" s="131"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="159" t="s">
+        <v>340</v>
+      </c>
+      <c r="B103" s="159"/>
+      <c r="C103" s="159"/>
+      <c r="D103" s="159"/>
+      <c r="E103" s="159"/>
+      <c r="F103" s="159"/>
+      <c r="G103" s="159"/>
+      <c r="H103" s="159"/>
+      <c r="I103" s="159"/>
+      <c r="J103" s="159"/>
+    </row>
+    <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="160" t="s">
+        <v>1</v>
+      </c>
+      <c r="B104" s="160" t="s">
+        <v>320</v>
+      </c>
+      <c r="C104" s="160" t="s">
+        <v>341</v>
+      </c>
+      <c r="D104" s="160" t="s">
+        <v>342</v>
+      </c>
+      <c r="E104" s="160" t="s">
+        <v>319</v>
+      </c>
+      <c r="F104" s="160" t="s">
+        <v>343</v>
+      </c>
+      <c r="G104" s="160" t="s">
+        <v>344</v>
+      </c>
+      <c r="H104" s="160" t="s">
+        <v>345</v>
+      </c>
+      <c r="I104" s="160" t="s">
+        <v>346</v>
+      </c>
+      <c r="J104" s="160" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B105" s="151" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="C105" s="151" t="n">
+        <v>50</v>
+      </c>
+      <c r="D105" s="161" t="n">
+        <f aca="false">B105+C105</f>
+        <v>76.5</v>
+      </c>
+      <c r="E105" s="151" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="F105" s="151" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G105" s="151" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H105" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I105" s="154" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="J105" s="27" t="n">
+        <f aca="false">D105/I105</f>
+        <v>0.174219995445229</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B106" s="151" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="C106" s="151" t="n">
+        <v>50</v>
+      </c>
+      <c r="D106" s="161" t="n">
+        <f aca="false">B106+C106</f>
+        <v>76.5</v>
+      </c>
+      <c r="E106" s="151" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="F106" s="151" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G106" s="151" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H106" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I106" s="154" t="n">
+        <v>437.8</v>
+      </c>
+      <c r="J106" s="27" t="n">
+        <f aca="false">D106/I106</f>
+        <v>0.174737322978529</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B107" s="151" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="C107" s="151" t="n">
+        <v>47</v>
+      </c>
+      <c r="D107" s="161" t="n">
+        <f aca="false">B107+C107</f>
+        <v>73.5</v>
+      </c>
+      <c r="E107" s="151" t="n">
+        <v>194.3</v>
+      </c>
+      <c r="F107" s="151" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G107" s="151" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H107" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I107" s="154" t="n">
+        <v>419.1</v>
+      </c>
+      <c r="J107" s="27" t="n">
+        <f aca="false">D107/I107</f>
+        <v>0.175375805297065</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="B108" s="151" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C108" s="151" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D108" s="161" t="n">
+        <f aca="false">B108+C108</f>
+        <v>81.1</v>
+      </c>
+      <c r="E108" s="151" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="F108" s="151" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G108" s="151" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H108" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I108" s="154" t="n">
+        <v>423.9</v>
+      </c>
+      <c r="J108" s="27" t="n">
+        <f aca="false">D108/I108</f>
+        <v>0.191318707242274</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B109" s="151" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="C109" s="151" t="n">
+        <v>51</v>
+      </c>
+      <c r="D109" s="161" t="n">
+        <f aca="false">B109+C109</f>
+        <v>75.3</v>
+      </c>
+      <c r="E109" s="151" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="F109" s="151" t="n">
+        <v>28</v>
+      </c>
+      <c r="G109" s="151" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H109" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I109" s="154" t="n">
+        <v>413.1</v>
+      </c>
+      <c r="J109" s="27" t="n">
+        <f aca="false">D109/I109</f>
+        <v>0.182280319535221</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="B110" s="151" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C110" s="151" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="D110" s="161" t="n">
+        <f aca="false">B110+C110</f>
+        <v>76.7</v>
+      </c>
+      <c r="E110" s="151" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="F110" s="151" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G110" s="151" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H110" s="151" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I110" s="154" t="n">
+        <v>418.1</v>
+      </c>
+      <c r="J110" s="27" t="n">
+        <f aca="false">D110/I110</f>
+        <v>0.183448935661325</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="B111" s="151" t="n">
+        <v>23</v>
+      </c>
+      <c r="C111" s="151" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="D111" s="161" t="n">
+        <f aca="false">B111+C111</f>
+        <v>78.5</v>
+      </c>
+      <c r="E111" s="151" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="F111" s="151" t="n">
+        <v>30</v>
+      </c>
+      <c r="G111" s="151" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H111" s="151" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I111" s="154" t="n">
+        <v>407.9</v>
+      </c>
+      <c r="J111" s="27" t="n">
+        <f aca="false">D111/I111</f>
+        <v>0.192449129688649</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="B112" s="151" t="n">
+        <v>24</v>
+      </c>
+      <c r="C112" s="151" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="D112" s="161" t="n">
+        <f aca="false">B112+C112</f>
+        <v>84.5</v>
+      </c>
+      <c r="E112" s="151" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="F112" s="151" t="n">
+        <v>31</v>
+      </c>
+      <c r="G112" s="151" t="n">
+        <v>16</v>
+      </c>
+      <c r="H112" s="151" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I112" s="154" t="n">
+        <v>421.3</v>
+      </c>
+      <c r="J112" s="27" t="n">
+        <f aca="false">D112/I112</f>
+        <v>0.200569665321624</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B113" s="151" t="n">
+        <v>24</v>
+      </c>
+      <c r="C113" s="151" t="n">
+        <v>57</v>
+      </c>
+      <c r="D113" s="161" t="n">
+        <f aca="false">B113+C113</f>
+        <v>81</v>
+      </c>
+      <c r="E113" s="151" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="F113" s="151" t="n">
+        <v>32</v>
+      </c>
+      <c r="G113" s="151" t="n">
+        <v>17</v>
+      </c>
+      <c r="H113" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I113" s="154" t="n">
+        <v>412.1</v>
+      </c>
+      <c r="J113" s="27" t="n">
+        <f aca="false">D113/I113</f>
+        <v>0.196554234409124</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="B114" s="151" t="n">
+        <v>24</v>
+      </c>
+      <c r="C114" s="151" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="D114" s="161" t="n">
+        <f aca="false">B114+C114</f>
+        <v>76.3</v>
+      </c>
+      <c r="E114" s="151" t="n">
+        <v>160.4</v>
+      </c>
+      <c r="F114" s="151" t="n">
+        <v>33</v>
+      </c>
+      <c r="G114" s="151" t="n">
+        <v>16</v>
+      </c>
+      <c r="H114" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I114" s="154" t="n">
+        <v>400.6</v>
+      </c>
+      <c r="J114" s="27" t="n">
+        <f aca="false">D114/I114</f>
+        <v>0.190464303544683</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B115" s="151" t="n">
+        <v>27</v>
+      </c>
+      <c r="C115" s="151" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D115" s="161" t="n">
+        <f aca="false">B115+C115</f>
+        <v>89.3</v>
+      </c>
+      <c r="E115" s="151" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="F115" s="151" t="n">
+        <v>33</v>
+      </c>
+      <c r="G115" s="151" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H115" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I115" s="154" t="n">
+        <v>423.2</v>
+      </c>
+      <c r="J115" s="27" t="n">
+        <f aca="false">D115/I115</f>
+        <v>0.211011342155009</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B116" s="151" t="n">
+        <v>26</v>
+      </c>
+      <c r="C116" s="151" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D116" s="161" t="n">
+        <f aca="false">B116+C116</f>
+        <v>88.3</v>
+      </c>
+      <c r="E116" s="151" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="F116" s="151" t="n">
+        <v>33</v>
+      </c>
+      <c r="G116" s="151" t="n">
+        <v>17</v>
+      </c>
+      <c r="H116" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I116" s="154" t="n">
+        <v>416.3</v>
+      </c>
+      <c r="J116" s="27" t="n">
+        <f aca="false">D116/I116</f>
+        <v>0.212106653855393</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="B117" s="151" t="n">
+        <v>26</v>
+      </c>
+      <c r="C117" s="151" t="n">
+        <v>62</v>
+      </c>
+      <c r="D117" s="161" t="n">
+        <f aca="false">B117+C117</f>
+        <v>88</v>
+      </c>
+      <c r="E117" s="151" t="n">
+        <v>160.8</v>
+      </c>
+      <c r="F117" s="151" t="n">
+        <v>33</v>
+      </c>
+      <c r="G117" s="151" t="n">
+        <v>18</v>
+      </c>
+      <c r="H117" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I117" s="154" t="n">
+        <v>419.3</v>
+      </c>
+      <c r="J117" s="27" t="n">
+        <f aca="false">D117/I117</f>
+        <v>0.209873598855235</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="B118" s="151" t="n">
+        <v>25</v>
+      </c>
+      <c r="C118" s="151" t="n">
+        <v>63</v>
+      </c>
+      <c r="D118" s="161" t="n">
+        <f aca="false">B118+C118</f>
+        <v>88</v>
+      </c>
+      <c r="E118" s="151" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="F118" s="151" t="n">
+        <v>33</v>
+      </c>
+      <c r="G118" s="151" t="n">
+        <v>16</v>
+      </c>
+      <c r="H118" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I118" s="154" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="J118" s="27" t="n">
+        <f aca="false">D118/I118</f>
+        <v>0.209923664122137</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="B119" s="151" t="n">
+        <v>26</v>
+      </c>
+      <c r="C119" s="151" t="n">
+        <v>61</v>
+      </c>
+      <c r="D119" s="161" t="n">
+        <f aca="false">B119+C119</f>
+        <v>87</v>
+      </c>
+      <c r="E119" s="151" t="n">
+        <v>161</v>
+      </c>
+      <c r="F119" s="151" t="n">
+        <v>34</v>
+      </c>
+      <c r="G119" s="151" t="n">
+        <v>15</v>
+      </c>
+      <c r="H119" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I119" s="154" t="n">
+        <v>418</v>
+      </c>
+      <c r="J119" s="27" t="n">
+        <f aca="false">D119/I119</f>
+        <v>0.208133971291866</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="B120" s="151" t="n">
+        <v>24</v>
+      </c>
+      <c r="C120" s="151" t="n">
+        <v>57</v>
+      </c>
+      <c r="D120" s="161" t="n">
+        <f aca="false">B120+C120</f>
+        <v>81</v>
+      </c>
+      <c r="E120" s="151" t="n">
+        <v>162.4</v>
+      </c>
+      <c r="F120" s="151" t="n">
+        <v>33</v>
+      </c>
+      <c r="G120" s="151" t="n">
+        <v>16</v>
+      </c>
+      <c r="H120" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I120" s="154" t="n">
+        <v>404.2</v>
+      </c>
+      <c r="J120" s="27" t="n">
+        <f aca="false">D120/I120</f>
+        <v>0.200395843641762</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B121" s="151" t="n">
+        <v>28</v>
+      </c>
+      <c r="C121" s="151" t="n">
+        <v>65</v>
+      </c>
+      <c r="D121" s="161" t="n">
+        <f aca="false">B121+C121</f>
+        <v>93</v>
+      </c>
+      <c r="E121" s="151" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="F121" s="162" t="n">
+        <v>89</v>
+      </c>
+      <c r="G121" s="151" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H121" s="151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I121" s="154" t="n">
+        <v>474.9</v>
+      </c>
+      <c r="J121" s="27" t="n">
+        <f aca="false">D121/I121</f>
+        <v>0.195830701200253</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="B123" s="27" t="n">
+        <f aca="false">(B121-B105)/B105</f>
+        <v>0.0566037735849057</v>
+      </c>
+      <c r="C123" s="27" t="n">
+        <f aca="false">(C121-C105)/C105</f>
+        <v>0.3</v>
+      </c>
+      <c r="D123" s="27" t="n">
+        <f aca="false">(D121-D105)/D105</f>
+        <v>0.215686274509804</v>
+      </c>
+      <c r="E123" s="27" t="n">
+        <f aca="false">(E121-E105)/E105</f>
+        <v>-0.212579229644076</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="81" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="158" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="158" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="158" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="158" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="158" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="158"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="158" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="158"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="158" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="163" t="s">
+        <v>356</v>
+      </c>
+      <c r="B137" s="163"/>
+      <c r="C137" s="163"/>
+      <c r="D137" s="163"/>
+      <c r="E137" s="163"/>
+      <c r="F137" s="163"/>
+    </row>
+    <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="B138" s="164" t="s">
+        <v>357</v>
+      </c>
+      <c r="C138" s="164" t="s">
+        <v>358</v>
+      </c>
+      <c r="D138" s="164" t="s">
+        <v>359</v>
+      </c>
+      <c r="E138" s="164" t="s">
+        <v>360</v>
+      </c>
+      <c r="F138" s="164" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="165" t="s">
+        <v>106</v>
+      </c>
+      <c r="B139" s="166" t="n">
+        <v>729106</v>
+      </c>
+      <c r="C139" s="166" t="n">
+        <v>1253249</v>
+      </c>
+      <c r="D139" s="167" t="n">
+        <v>16884485</v>
+      </c>
+      <c r="E139" s="168" t="n">
+        <f aca="false">C139/D139</f>
+        <v>0.07422488752248</v>
+      </c>
+      <c r="F139" s="167" t="n">
+        <v>729106</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="165" t="s">
+        <v>107</v>
+      </c>
+      <c r="B140" s="166" t="n">
+        <v>714526</v>
+      </c>
+      <c r="C140" s="166" t="n">
+        <v>1343683</v>
+      </c>
+      <c r="D140" s="167" t="n">
+        <v>16432127</v>
+      </c>
+      <c r="E140" s="168" t="n">
+        <f aca="false">C140/D140</f>
+        <v>0.0817717024704106</v>
+      </c>
+      <c r="F140" s="167" t="n">
+        <v>756812</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="165" t="s">
+        <v>108</v>
+      </c>
+      <c r="B141" s="166" t="n">
+        <v>782570</v>
+      </c>
+      <c r="C141" s="166" t="n">
+        <v>1588585</v>
+      </c>
+      <c r="D141" s="167" t="n">
+        <v>16504036</v>
+      </c>
+      <c r="E141" s="168" t="n">
+        <f aca="false">C141/D141</f>
+        <v>0.0962543343943263</v>
+      </c>
+      <c r="F141" s="167" t="n">
+        <v>754625</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="165" t="s">
+        <v>109</v>
+      </c>
+      <c r="B142" s="166" t="n">
+        <v>1016477</v>
+      </c>
+      <c r="C142" s="166" t="n">
+        <v>1696379</v>
+      </c>
+      <c r="D142" s="167" t="n">
+        <v>16784880</v>
+      </c>
+      <c r="E142" s="168" t="n">
+        <f aca="false">C142/D142</f>
+        <v>0.101065899785998</v>
+      </c>
+      <c r="F142" s="167" t="n">
+        <v>767020</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="165" t="s">
+        <v>110</v>
+      </c>
+      <c r="B143" s="166" t="n">
+        <v>1045629</v>
+      </c>
+      <c r="C143" s="166" t="n">
+        <v>1737763</v>
+      </c>
+      <c r="D143" s="167" t="n">
+        <v>16893940</v>
+      </c>
+      <c r="E143" s="168" t="n">
+        <f aca="false">C143/D143</f>
+        <v>0.102863097655136</v>
+      </c>
+      <c r="F143" s="167" t="n">
+        <v>791080</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="165" t="s">
+        <v>111</v>
+      </c>
+      <c r="B144" s="166" t="n">
+        <v>1122201</v>
+      </c>
+      <c r="C144" s="166" t="n">
+        <v>1350978</v>
+      </c>
+      <c r="D144" s="167" t="n">
+        <v>15772924</v>
+      </c>
+      <c r="E144" s="168" t="n">
+        <f aca="false">C144/D144</f>
+        <v>0.0856517155601587</v>
+      </c>
+      <c r="F144" s="167" t="n">
+        <v>807120</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="165" t="s">
+        <v>112</v>
+      </c>
+      <c r="B145" s="166" t="n">
+        <v>1002760</v>
+      </c>
+      <c r="C145" s="166" t="n">
+        <v>1567296</v>
+      </c>
+      <c r="D145" s="167" t="n">
+        <v>16233804</v>
+      </c>
+      <c r="E145" s="168" t="n">
+        <f aca="false">C145/D145</f>
+        <v>0.0965452089972258</v>
+      </c>
+      <c r="F145" s="167" t="n">
+        <v>818786</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="165" t="s">
+        <v>113</v>
+      </c>
+      <c r="B146" s="166" t="n">
+        <v>941618</v>
+      </c>
+      <c r="C146" s="166" t="n">
+        <v>1516957</v>
+      </c>
+      <c r="D146" s="167" t="n">
+        <v>16445568</v>
+      </c>
+      <c r="E146" s="168" t="n">
+        <f aca="false">C146/D146</f>
+        <v>0.0922410828254761</v>
+      </c>
+      <c r="F146" s="167" t="n">
+        <v>832639</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="165" t="s">
+        <v>114</v>
+      </c>
+      <c r="B147" s="166" t="n">
+        <v>782635</v>
+      </c>
+      <c r="C147" s="166" t="n">
+        <v>1395486</v>
+      </c>
+      <c r="D147" s="167" t="n">
+        <v>16990456</v>
+      </c>
+      <c r="E147" s="168" t="n">
+        <f aca="false">C147/D147</f>
+        <v>0.0821335224905088</v>
+      </c>
+      <c r="F147" s="167" t="n">
+        <v>833368</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="165" t="s">
+        <v>115</v>
+      </c>
+      <c r="B148" s="166" t="n">
+        <v>1004860</v>
+      </c>
+      <c r="C148" s="166" t="n">
+        <v>1657614</v>
+      </c>
+      <c r="D148" s="167" t="n">
+        <v>17265540</v>
+      </c>
+      <c r="E148" s="168" t="n">
+        <f aca="false">C148/D148</f>
+        <v>0.0960070753651493</v>
+      </c>
+      <c r="F148" s="167" t="n">
+        <v>843576</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="165" t="s">
+        <v>116</v>
+      </c>
+      <c r="B149" s="166" t="n">
+        <v>860562</v>
+      </c>
+      <c r="C149" s="166" t="n">
+        <v>1579325</v>
+      </c>
+      <c r="D149" s="167" t="n">
+        <v>17850000</v>
+      </c>
+      <c r="E149" s="168" t="n">
+        <f aca="false">C149/D149</f>
+        <v>0.0884775910364146</v>
+      </c>
+      <c r="F149" s="167" t="n">
+        <v>861803</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="165" t="s">
+        <v>117</v>
+      </c>
+      <c r="B150" s="166" t="n">
+        <v>874951</v>
+      </c>
+      <c r="C150" s="166" t="n">
+        <v>1642333</v>
+      </c>
+      <c r="D150" s="167" t="n">
+        <v>17951144</v>
+      </c>
+      <c r="E150" s="168" t="n">
+        <f aca="false">C150/D150</f>
+        <v>0.091489043818043</v>
+      </c>
+      <c r="F150" s="167" t="n">
+        <v>882947</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="165" t="s">
+        <v>118</v>
+      </c>
+      <c r="B151" s="166" t="n">
+        <v>916343</v>
+      </c>
+      <c r="C151" s="166" t="n">
+        <v>1683540</v>
+      </c>
+      <c r="D151" s="167" t="n">
+        <v>18092760</v>
+      </c>
+      <c r="E151" s="168" t="n">
+        <f aca="false">C151/D151</f>
+        <v>0.0930504798604525</v>
+      </c>
+      <c r="F151" s="167" t="n">
+        <v>898988</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="165" t="s">
+        <v>119</v>
+      </c>
+      <c r="B152" s="166" t="n">
+        <v>1045603</v>
+      </c>
+      <c r="C152" s="166" t="n">
+        <v>1721911</v>
+      </c>
+      <c r="D152" s="167" t="n">
+        <v>18268856</v>
+      </c>
+      <c r="E152" s="168" t="n">
+        <f aca="false">C152/D152</f>
+        <v>0.0942539040211385</v>
+      </c>
+      <c r="F152" s="167" t="n">
+        <v>909924</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="165" t="s">
+        <v>120</v>
+      </c>
+      <c r="B153" s="166" t="n">
+        <v>1118393</v>
+      </c>
+      <c r="C153" s="166" t="n">
+        <v>1863938</v>
+      </c>
+      <c r="D153" s="167" t="n">
+        <v>18737000</v>
+      </c>
+      <c r="E153" s="168" t="n">
+        <f aca="false">C153/D153</f>
+        <v>0.0994789987724823</v>
+      </c>
+      <c r="F153" s="167" t="n">
+        <v>952942</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="165" t="s">
+        <v>121</v>
+      </c>
+      <c r="B154" s="166" t="n">
+        <v>1096201</v>
+      </c>
+      <c r="C154" s="166" t="n">
+        <v>1842053</v>
+      </c>
+      <c r="D154" s="167" t="n">
+        <v>18797000</v>
+      </c>
+      <c r="E154" s="168" t="n">
+        <f aca="false">C154/D154</f>
+        <v>0.0979971804011278</v>
+      </c>
+      <c r="F154" s="167" t="n">
+        <v>1028769</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="165" t="s">
+        <v>122</v>
+      </c>
+      <c r="B155" s="166" t="n">
+        <v>1087399</v>
+      </c>
+      <c r="C155" s="169" t="n">
+        <v>1933000</v>
+      </c>
+      <c r="D155" s="167" t="n">
+        <v>19186700</v>
+      </c>
+      <c r="E155" s="168" t="n">
+        <f aca="false">C155/D155</f>
+        <v>0.1007468715308</v>
+      </c>
+      <c r="F155" s="167" t="n">
+        <v>1071057</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="165" t="s">
+        <v>123</v>
+      </c>
+      <c r="B156" s="166" t="n">
+        <v>1123290</v>
+      </c>
+      <c r="C156" s="166" t="n">
+        <v>2023725</v>
+      </c>
+      <c r="D156" s="167" t="n">
+        <v>20474019</v>
+      </c>
+      <c r="E156" s="168" t="n">
+        <f aca="false">C156/D156</f>
+        <v>0.0988435636403385</v>
+      </c>
+      <c r="F156" s="167" t="n">
+        <v>1103137</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="170" t="s">
+        <v>362</v>
+      </c>
+      <c r="B158" s="168" t="n">
+        <f aca="false">(B156-B139)/B139</f>
+        <v>0.540640181263081</v>
+      </c>
+      <c r="C158" s="168" t="n">
+        <f aca="false">(C156-C139)/C139</f>
+        <v>0.614782856399646</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="171" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="172" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="172" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="172" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="172" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="172" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="172" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="172"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="172" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="172" t="s">
+        <v>370</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A103:J103"/>
+    <mergeCell ref="A137:F137"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
